--- a/diseases/d040/2026-2029.xlsx
+++ b/diseases/d040/2026-2029.xlsx
@@ -66005,12 +66005,12 @@
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
@@ -66035,7 +66035,7 @@
       </c>
       <c r="L355" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M355" t="inlineStr">
@@ -66049,9 +66049,6 @@
       <c r="O355" t="n">
         <v>0</v>
       </c>
-      <c r="P355" t="n">
-        <v>0</v>
-      </c>
       <c r="R355" t="n">
         <v>0</v>
       </c>
@@ -66062,12 +66059,12 @@
       </c>
       <c r="U355" t="inlineStr">
         <is>
-          <t>SER_JP_RUBELLA_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_RUBELLA</t>
         </is>
       </c>
       <c r="AA355" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO355" t="inlineStr">
@@ -66077,7 +66074,7 @@
       </c>
       <c r="AP355" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ355" t="inlineStr">
@@ -66085,57 +66082,62 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR355" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS355" t="inlineStr">
         <is>
-          <t>SER_JP_RUBELLA_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_RUBELLA</t>
         </is>
       </c>
       <c r="AT355" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU355" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV355" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW355" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX355" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY355" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ355" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA355" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB355" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC355" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -66167,12 +66169,12 @@
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
@@ -66197,7 +66199,7 @@
       </c>
       <c r="L356" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M356" t="inlineStr">
@@ -66211,27 +66213,24 @@
       <c r="O356" t="n">
         <v>0</v>
       </c>
-      <c r="P356" t="n">
-        <v>0</v>
-      </c>
       <c r="U356" t="inlineStr">
         <is>
-          <t>SER_JP_RUBELLA_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_RUBELLA</t>
         </is>
       </c>
       <c r="V356" t="inlineStr">
         <is>
-          <t>SER_JP_RUBELLA_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_RUBELLA</t>
         </is>
       </c>
       <c r="W356" t="inlineStr">
         <is>
-          <t>SRC_JP_NIID</t>
+          <t>SRC_SE_FOHM_SMINET</t>
         </is>
       </c>
       <c r="X356" t="inlineStr">
         <is>
-          <t>Rubella</t>
+          <t>Röda hund</t>
         </is>
       </c>
       <c r="Y356" t="inlineStr">
@@ -66241,12 +66240,12 @@
       </c>
       <c r="Z356" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA356" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AB356" t="inlineStr">
@@ -66256,7 +66255,7 @@
       </c>
       <c r="AC356" t="inlineStr">
         <is>
-          <t>country:JP:national</t>
+          <t>country:SE:national</t>
         </is>
       </c>
       <c r="AD356" t="inlineStr">
@@ -66271,7 +66270,7 @@
       </c>
       <c r="AF356" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG356" t="inlineStr">
@@ -66291,17 +66290,17 @@
       </c>
       <c r="AJ356" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>SE_FOHM_SMINET_current</t>
         </is>
       </c>
       <c r="AK356" t="inlineStr">
         <is>
-          <t>Japan NIID rubella notifications, excluding congenital rubella syndrome.</t>
+          <t>Sweden FHM SmiNet national monthly notification series; Excludes congenital rubella syndrome unless source definition changes.</t>
         </is>
       </c>
       <c r="AM356" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>revised</t>
         </is>
       </c>
       <c r="AN356" t="b">
@@ -66314,7 +66313,7 @@
       </c>
       <c r="AP356" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ356" t="inlineStr">
@@ -66322,57 +66321,62 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR356" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS356" t="inlineStr">
         <is>
-          <t>SER_JP_RUBELLA_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_RUBELLA</t>
         </is>
       </c>
       <c r="AT356" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU356" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV356" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW356" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX356" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY356" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ356" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA356" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB356" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC356" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -66404,12 +66408,12 @@
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
@@ -66459,6 +66463,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U357" t="inlineStr">
+        <is>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
+        </is>
+      </c>
       <c r="AA357" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -66471,7 +66480,7 @@
       </c>
       <c r="AP357" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ357" t="inlineStr">
@@ -66481,55 +66490,55 @@
       </c>
       <c r="AS357" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_RUBELLA; SER_SG_HIST_RUBELLA</t>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
         </is>
       </c>
       <c r="AT357" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU357" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV357" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW357" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX357" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY357" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ357" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA357" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB357" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC357" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -66561,12 +66570,12 @@
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H358" t="inlineStr">
@@ -66610,17 +66619,17 @@
       </c>
       <c r="U358" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_RUBELLA</t>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
         </is>
       </c>
       <c r="V358" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_RUBELLA</t>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
         </is>
       </c>
       <c r="W358" t="inlineStr">
         <is>
-          <t>SRC_SG_CDA_WIDB</t>
+          <t>SRC_JP_NIID</t>
         </is>
       </c>
       <c r="X358" t="inlineStr">
@@ -66635,7 +66644,7 @@
       </c>
       <c r="Z358" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_surveillance</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA358" t="inlineStr">
@@ -66650,7 +66659,7 @@
       </c>
       <c r="AC358" t="inlineStr">
         <is>
-          <t>country:SG:national</t>
+          <t>country:JP:national</t>
         </is>
       </c>
       <c r="AD358" t="inlineStr">
@@ -66665,7 +66674,7 @@
       </c>
       <c r="AF358" t="inlineStr">
         <is>
-          <t>conditional</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AG358" t="inlineStr">
@@ -66685,12 +66694,12 @@
       </c>
       <c r="AJ358" t="inlineStr">
         <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK358" t="inlineStr">
         <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+          <t>Japan NIID rubella notifications, excluding congenital rubella syndrome.</t>
         </is>
       </c>
       <c r="AM358" t="inlineStr">
@@ -66708,7 +66717,7 @@
       </c>
       <c r="AP358" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ358" t="inlineStr">
@@ -66718,55 +66727,55 @@
       </c>
       <c r="AS358" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_RUBELLA; SER_SG_HIST_RUBELLA</t>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
         </is>
       </c>
       <c r="AT358" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU358" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV358" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW358" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX358" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY358" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ358" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA358" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB358" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC358" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -66798,12 +66807,12 @@
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
@@ -66828,7 +66837,7 @@
       </c>
       <c r="L359" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M359" t="inlineStr">
@@ -66853,11 +66862,6 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U359" t="inlineStr">
-        <is>
-          <t>SER_JP_RUBELLA_WEEKLY</t>
-        </is>
-      </c>
       <c r="AA359" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -66870,7 +66874,7 @@
       </c>
       <c r="AP359" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ359" t="inlineStr">
@@ -66880,55 +66884,55 @@
       </c>
       <c r="AS359" t="inlineStr">
         <is>
-          <t>SER_JP_RUBELLA_WEEKLY</t>
+          <t>SER_SG_CDA_RUBELLA; SER_SG_HIST_RUBELLA</t>
         </is>
       </c>
       <c r="AT359" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU359" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV359" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW359" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX359" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY359" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ359" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA359" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB359" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC359" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -66960,12 +66964,12 @@
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H360" t="inlineStr">
@@ -66990,7 +66994,7 @@
       </c>
       <c r="L360" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M360" t="inlineStr">
@@ -67009,17 +67013,17 @@
       </c>
       <c r="U360" t="inlineStr">
         <is>
-          <t>SER_JP_RUBELLA_WEEKLY</t>
+          <t>SER_SG_CDA_RUBELLA</t>
         </is>
       </c>
       <c r="V360" t="inlineStr">
         <is>
-          <t>SER_JP_RUBELLA_WEEKLY</t>
+          <t>SER_SG_CDA_RUBELLA</t>
         </is>
       </c>
       <c r="W360" t="inlineStr">
         <is>
-          <t>SRC_JP_NIID</t>
+          <t>SRC_SG_CDA_WIDB</t>
         </is>
       </c>
       <c r="X360" t="inlineStr">
@@ -67034,7 +67038,7 @@
       </c>
       <c r="Z360" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA360" t="inlineStr">
@@ -67049,7 +67053,7 @@
       </c>
       <c r="AC360" t="inlineStr">
         <is>
-          <t>country:JP:national</t>
+          <t>country:SG:national</t>
         </is>
       </c>
       <c r="AD360" t="inlineStr">
@@ -67064,7 +67068,7 @@
       </c>
       <c r="AF360" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG360" t="inlineStr">
@@ -67084,12 +67088,12 @@
       </c>
       <c r="AJ360" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
         </is>
       </c>
       <c r="AK360" t="inlineStr">
         <is>
-          <t>Japan NIID rubella notifications, excluding congenital rubella syndrome.</t>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
         </is>
       </c>
       <c r="AM360" t="inlineStr">
@@ -67107,7 +67111,7 @@
       </c>
       <c r="AP360" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ360" t="inlineStr">
@@ -67117,55 +67121,55 @@
       </c>
       <c r="AS360" t="inlineStr">
         <is>
-          <t>SER_JP_RUBELLA_WEEKLY</t>
+          <t>SER_SG_CDA_RUBELLA; SER_SG_HIST_RUBELLA</t>
         </is>
       </c>
       <c r="AT360" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU360" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV360" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW360" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX360" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY360" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ360" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA360" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB360" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC360" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -67197,12 +67201,12 @@
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H361" t="inlineStr">
@@ -67252,6 +67256,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U361" t="inlineStr">
+        <is>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
+        </is>
+      </c>
       <c r="AA361" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -67264,7 +67273,7 @@
       </c>
       <c r="AP361" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ361" t="inlineStr">
@@ -67274,55 +67283,55 @@
       </c>
       <c r="AS361" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_RUBELLA; SER_SG_HIST_RUBELLA</t>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
         </is>
       </c>
       <c r="AT361" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU361" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV361" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW361" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX361" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY361" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ361" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA361" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB361" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC361" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -67354,12 +67363,12 @@
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
@@ -67403,17 +67412,17 @@
       </c>
       <c r="U362" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_RUBELLA</t>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
         </is>
       </c>
       <c r="V362" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_RUBELLA</t>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
         </is>
       </c>
       <c r="W362" t="inlineStr">
         <is>
-          <t>SRC_SG_CDA_WIDB</t>
+          <t>SRC_JP_NIID</t>
         </is>
       </c>
       <c r="X362" t="inlineStr">
@@ -67428,7 +67437,7 @@
       </c>
       <c r="Z362" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_surveillance</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA362" t="inlineStr">
@@ -67443,7 +67452,7 @@
       </c>
       <c r="AC362" t="inlineStr">
         <is>
-          <t>country:SG:national</t>
+          <t>country:JP:national</t>
         </is>
       </c>
       <c r="AD362" t="inlineStr">
@@ -67458,7 +67467,7 @@
       </c>
       <c r="AF362" t="inlineStr">
         <is>
-          <t>conditional</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AG362" t="inlineStr">
@@ -67478,12 +67487,12 @@
       </c>
       <c r="AJ362" t="inlineStr">
         <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK362" t="inlineStr">
         <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+          <t>Japan NIID rubella notifications, excluding congenital rubella syndrome.</t>
         </is>
       </c>
       <c r="AM362" t="inlineStr">
@@ -67501,7 +67510,7 @@
       </c>
       <c r="AP362" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ362" t="inlineStr">
@@ -67511,55 +67520,55 @@
       </c>
       <c r="AS362" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_RUBELLA; SER_SG_HIST_RUBELLA</t>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
         </is>
       </c>
       <c r="AT362" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU362" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV362" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW362" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX362" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY362" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ362" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA362" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB362" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC362" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -67591,12 +67600,12 @@
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
@@ -67621,7 +67630,7 @@
       </c>
       <c r="L363" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M363" t="inlineStr">
@@ -67646,11 +67655,6 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U363" t="inlineStr">
-        <is>
-          <t>SER_JP_RUBELLA_WEEKLY</t>
-        </is>
-      </c>
       <c r="AA363" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -67663,7 +67667,7 @@
       </c>
       <c r="AP363" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ363" t="inlineStr">
@@ -67673,55 +67677,55 @@
       </c>
       <c r="AS363" t="inlineStr">
         <is>
-          <t>SER_JP_RUBELLA_WEEKLY</t>
+          <t>SER_SG_CDA_RUBELLA; SER_SG_HIST_RUBELLA</t>
         </is>
       </c>
       <c r="AT363" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU363" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV363" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW363" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX363" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY363" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ363" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA363" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB363" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC363" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -67753,12 +67757,12 @@
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
@@ -67783,7 +67787,7 @@
       </c>
       <c r="L364" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M364" t="inlineStr">
@@ -67802,17 +67806,17 @@
       </c>
       <c r="U364" t="inlineStr">
         <is>
-          <t>SER_JP_RUBELLA_WEEKLY</t>
+          <t>SER_SG_CDA_RUBELLA</t>
         </is>
       </c>
       <c r="V364" t="inlineStr">
         <is>
-          <t>SER_JP_RUBELLA_WEEKLY</t>
+          <t>SER_SG_CDA_RUBELLA</t>
         </is>
       </c>
       <c r="W364" t="inlineStr">
         <is>
-          <t>SRC_JP_NIID</t>
+          <t>SRC_SG_CDA_WIDB</t>
         </is>
       </c>
       <c r="X364" t="inlineStr">
@@ -67827,7 +67831,7 @@
       </c>
       <c r="Z364" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA364" t="inlineStr">
@@ -67842,7 +67846,7 @@
       </c>
       <c r="AC364" t="inlineStr">
         <is>
-          <t>country:JP:national</t>
+          <t>country:SG:national</t>
         </is>
       </c>
       <c r="AD364" t="inlineStr">
@@ -67857,7 +67861,7 @@
       </c>
       <c r="AF364" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG364" t="inlineStr">
@@ -67877,12 +67881,12 @@
       </c>
       <c r="AJ364" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
         </is>
       </c>
       <c r="AK364" t="inlineStr">
         <is>
-          <t>Japan NIID rubella notifications, excluding congenital rubella syndrome.</t>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
         </is>
       </c>
       <c r="AM364" t="inlineStr">
@@ -67900,7 +67904,7 @@
       </c>
       <c r="AP364" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ364" t="inlineStr">
@@ -67910,55 +67914,55 @@
       </c>
       <c r="AS364" t="inlineStr">
         <is>
-          <t>SER_JP_RUBELLA_WEEKLY</t>
+          <t>SER_SG_CDA_RUBELLA; SER_SG_HIST_RUBELLA</t>
         </is>
       </c>
       <c r="AT364" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU364" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV364" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW364" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX364" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY364" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ364" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA364" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB364" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC364" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -67990,12 +67994,12 @@
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H365" t="inlineStr">
@@ -68045,6 +68049,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U365" t="inlineStr">
+        <is>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
+        </is>
+      </c>
       <c r="AA365" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -68057,7 +68066,7 @@
       </c>
       <c r="AP365" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ365" t="inlineStr">
@@ -68067,55 +68076,55 @@
       </c>
       <c r="AS365" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_RUBELLA; SER_SG_HIST_RUBELLA</t>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
         </is>
       </c>
       <c r="AT365" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU365" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV365" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW365" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX365" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY365" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ365" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA365" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB365" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC365" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -68147,12 +68156,12 @@
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H366" t="inlineStr">
@@ -68196,17 +68205,17 @@
       </c>
       <c r="U366" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_RUBELLA</t>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
         </is>
       </c>
       <c r="V366" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_RUBELLA</t>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
         </is>
       </c>
       <c r="W366" t="inlineStr">
         <is>
-          <t>SRC_SG_CDA_WIDB</t>
+          <t>SRC_JP_NIID</t>
         </is>
       </c>
       <c r="X366" t="inlineStr">
@@ -68221,7 +68230,7 @@
       </c>
       <c r="Z366" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_surveillance</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA366" t="inlineStr">
@@ -68236,7 +68245,7 @@
       </c>
       <c r="AC366" t="inlineStr">
         <is>
-          <t>country:SG:national</t>
+          <t>country:JP:national</t>
         </is>
       </c>
       <c r="AD366" t="inlineStr">
@@ -68251,7 +68260,7 @@
       </c>
       <c r="AF366" t="inlineStr">
         <is>
-          <t>conditional</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AG366" t="inlineStr">
@@ -68271,12 +68280,12 @@
       </c>
       <c r="AJ366" t="inlineStr">
         <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK366" t="inlineStr">
         <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+          <t>Japan NIID rubella notifications, excluding congenital rubella syndrome.</t>
         </is>
       </c>
       <c r="AM366" t="inlineStr">
@@ -68294,7 +68303,7 @@
       </c>
       <c r="AP366" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ366" t="inlineStr">
@@ -68304,55 +68313,55 @@
       </c>
       <c r="AS366" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_RUBELLA; SER_SG_HIST_RUBELLA</t>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
         </is>
       </c>
       <c r="AT366" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU366" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV366" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW366" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX366" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY366" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ366" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA366" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB366" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC366" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -68384,12 +68393,12 @@
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H367" t="inlineStr">
@@ -68414,7 +68423,7 @@
       </c>
       <c r="L367" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M367" t="inlineStr">
@@ -68439,11 +68448,6 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U367" t="inlineStr">
-        <is>
-          <t>SER_JP_RUBELLA_WEEKLY</t>
-        </is>
-      </c>
       <c r="AA367" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -68456,7 +68460,7 @@
       </c>
       <c r="AP367" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ367" t="inlineStr">
@@ -68466,55 +68470,55 @@
       </c>
       <c r="AS367" t="inlineStr">
         <is>
-          <t>SER_JP_RUBELLA_WEEKLY</t>
+          <t>SER_SG_CDA_RUBELLA; SER_SG_HIST_RUBELLA</t>
         </is>
       </c>
       <c r="AT367" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU367" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV367" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW367" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX367" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY367" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ367" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA367" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB367" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC367" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -68546,12 +68550,12 @@
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H368" t="inlineStr">
@@ -68576,7 +68580,7 @@
       </c>
       <c r="L368" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M368" t="inlineStr">
@@ -68595,17 +68599,17 @@
       </c>
       <c r="U368" t="inlineStr">
         <is>
-          <t>SER_JP_RUBELLA_WEEKLY</t>
+          <t>SER_SG_CDA_RUBELLA</t>
         </is>
       </c>
       <c r="V368" t="inlineStr">
         <is>
-          <t>SER_JP_RUBELLA_WEEKLY</t>
+          <t>SER_SG_CDA_RUBELLA</t>
         </is>
       </c>
       <c r="W368" t="inlineStr">
         <is>
-          <t>SRC_JP_NIID</t>
+          <t>SRC_SG_CDA_WIDB</t>
         </is>
       </c>
       <c r="X368" t="inlineStr">
@@ -68620,7 +68624,7 @@
       </c>
       <c r="Z368" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA368" t="inlineStr">
@@ -68635,7 +68639,7 @@
       </c>
       <c r="AC368" t="inlineStr">
         <is>
-          <t>country:JP:national</t>
+          <t>country:SG:national</t>
         </is>
       </c>
       <c r="AD368" t="inlineStr">
@@ -68650,7 +68654,7 @@
       </c>
       <c r="AF368" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG368" t="inlineStr">
@@ -68670,12 +68674,12 @@
       </c>
       <c r="AJ368" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
         </is>
       </c>
       <c r="AK368" t="inlineStr">
         <is>
-          <t>Japan NIID rubella notifications, excluding congenital rubella syndrome.</t>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
         </is>
       </c>
       <c r="AM368" t="inlineStr">
@@ -68693,7 +68697,7 @@
       </c>
       <c r="AP368" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ368" t="inlineStr">
@@ -68703,55 +68707,55 @@
       </c>
       <c r="AS368" t="inlineStr">
         <is>
-          <t>SER_JP_RUBELLA_WEEKLY</t>
+          <t>SER_SG_CDA_RUBELLA; SER_SG_HIST_RUBELLA</t>
         </is>
       </c>
       <c r="AT368" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU368" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV368" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW368" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX368" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY368" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ368" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA368" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB368" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC368" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -68783,12 +68787,12 @@
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H369" t="inlineStr">
@@ -68838,6 +68842,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U369" t="inlineStr">
+        <is>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
+        </is>
+      </c>
       <c r="AA369" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -68850,7 +68859,7 @@
       </c>
       <c r="AP369" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ369" t="inlineStr">
@@ -68860,55 +68869,55 @@
       </c>
       <c r="AS369" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_RUBELLA; SER_SG_HIST_RUBELLA</t>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
         </is>
       </c>
       <c r="AT369" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU369" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV369" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW369" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX369" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY369" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ369" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA369" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB369" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC369" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -68940,12 +68949,12 @@
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H370" t="inlineStr">
@@ -68989,17 +68998,17 @@
       </c>
       <c r="U370" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_RUBELLA</t>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
         </is>
       </c>
       <c r="V370" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_RUBELLA</t>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
         </is>
       </c>
       <c r="W370" t="inlineStr">
         <is>
-          <t>SRC_SG_CDA_WIDB</t>
+          <t>SRC_JP_NIID</t>
         </is>
       </c>
       <c r="X370" t="inlineStr">
@@ -69014,7 +69023,7 @@
       </c>
       <c r="Z370" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_surveillance</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA370" t="inlineStr">
@@ -69029,7 +69038,7 @@
       </c>
       <c r="AC370" t="inlineStr">
         <is>
-          <t>country:SG:national</t>
+          <t>country:JP:national</t>
         </is>
       </c>
       <c r="AD370" t="inlineStr">
@@ -69044,7 +69053,7 @@
       </c>
       <c r="AF370" t="inlineStr">
         <is>
-          <t>conditional</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AG370" t="inlineStr">
@@ -69064,12 +69073,12 @@
       </c>
       <c r="AJ370" t="inlineStr">
         <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK370" t="inlineStr">
         <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+          <t>Japan NIID rubella notifications, excluding congenital rubella syndrome.</t>
         </is>
       </c>
       <c r="AM370" t="inlineStr">
@@ -69087,7 +69096,7 @@
       </c>
       <c r="AP370" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ370" t="inlineStr">
@@ -69097,55 +69106,55 @@
       </c>
       <c r="AS370" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_RUBELLA; SER_SG_HIST_RUBELLA</t>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
         </is>
       </c>
       <c r="AT370" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU370" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV370" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW370" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX370" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY370" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ370" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA370" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB370" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC370" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -69177,12 +69186,12 @@
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H371" t="inlineStr">
@@ -69207,12 +69216,12 @@
       </c>
       <c r="L371" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N371" t="n">
@@ -69221,6 +69230,9 @@
       <c r="O371" t="n">
         <v>0</v>
       </c>
+      <c r="P371" t="n">
+        <v>0</v>
+      </c>
       <c r="R371" t="n">
         <v>0</v>
       </c>
@@ -69229,82 +69241,77 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U371" t="inlineStr">
-        <is>
-          <t>SER_AU_RUBELLA</t>
-        </is>
-      </c>
       <c r="AA371" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO371" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP371" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ371" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS371" t="inlineStr">
         <is>
-          <t>SER_AU_RUBELLA</t>
+          <t>SER_SG_CDA_RUBELLA; SER_SG_HIST_RUBELLA</t>
         </is>
       </c>
       <c r="AT371" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU371" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV371" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW371" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX371" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY371" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ371" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA371" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB371" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC371" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -69336,12 +69343,12 @@
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H372" t="inlineStr">
@@ -69366,12 +69373,12 @@
       </c>
       <c r="L372" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N372" t="n">
@@ -69380,19 +69387,22 @@
       <c r="O372" t="n">
         <v>0</v>
       </c>
+      <c r="P372" t="n">
+        <v>0</v>
+      </c>
       <c r="U372" t="inlineStr">
         <is>
-          <t>SER_AU_RUBELLA</t>
+          <t>SER_SG_CDA_RUBELLA</t>
         </is>
       </c>
       <c r="V372" t="inlineStr">
         <is>
-          <t>SER_AU_RUBELLA</t>
+          <t>SER_SG_CDA_RUBELLA</t>
         </is>
       </c>
       <c r="W372" t="inlineStr">
         <is>
-          <t>SRC_AU_NINDSS</t>
+          <t>SRC_SG_CDA_WIDB</t>
         </is>
       </c>
       <c r="X372" t="inlineStr">
@@ -69407,12 +69417,12 @@
       </c>
       <c r="Z372" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA372" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AB372" t="inlineStr">
@@ -69422,7 +69432,7 @@
       </c>
       <c r="AC372" t="inlineStr">
         <is>
-          <t>country:AU:national</t>
+          <t>country:SG:national</t>
         </is>
       </c>
       <c r="AD372" t="inlineStr">
@@ -69437,7 +69447,7 @@
       </c>
       <c r="AF372" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG372" t="inlineStr">
@@ -69457,12 +69467,12 @@
       </c>
       <c r="AJ372" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
         </is>
       </c>
       <c r="AK372" t="inlineStr">
         <is>
-          <t>Australia NINDSS rubella notifications excluding the separately reported congenital category.</t>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
         </is>
       </c>
       <c r="AM372" t="inlineStr">
@@ -69475,70 +69485,70 @@
       </c>
       <c r="AO372" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP372" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ372" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS372" t="inlineStr">
         <is>
-          <t>SER_AU_RUBELLA</t>
+          <t>SER_SG_CDA_RUBELLA; SER_SG_HIST_RUBELLA</t>
         </is>
       </c>
       <c r="AT372" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU372" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV372" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW372" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX372" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY372" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ372" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA372" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB372" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC372" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -69570,12 +69580,12 @@
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H373" t="inlineStr">
@@ -69624,7 +69634,7 @@
       </c>
       <c r="U373" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_172</t>
+          <t>SER_AU_RUBELLA</t>
         </is>
       </c>
       <c r="AA373" t="inlineStr">
@@ -69634,75 +69644,70 @@
       </c>
       <c r="AO373" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP373" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ373" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR373" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS373" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_172</t>
+          <t>SER_AU_RUBELLA</t>
         </is>
       </c>
       <c r="AT373" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU373" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV373" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW373" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX373" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY373" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ373" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA373" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB373" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC373" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -69734,12 +69739,12 @@
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
@@ -69780,22 +69785,22 @@
       </c>
       <c r="U374" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_172</t>
+          <t>SER_AU_RUBELLA</t>
         </is>
       </c>
       <c r="V374" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_172</t>
+          <t>SER_AU_RUBELLA</t>
         </is>
       </c>
       <c r="W374" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_AU_NINDSS</t>
         </is>
       </c>
       <c r="X374" t="inlineStr">
         <is>
-          <t>German measles</t>
+          <t>Rubella</t>
         </is>
       </c>
       <c r="Y374" t="inlineStr">
@@ -69805,7 +69810,7 @@
       </c>
       <c r="Z374" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA374" t="inlineStr">
@@ -69820,7 +69825,7 @@
       </c>
       <c r="AC374" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:AU:national</t>
         </is>
       </c>
       <c r="AD374" t="inlineStr">
@@ -69835,7 +69840,7 @@
       </c>
       <c r="AF374" t="inlineStr">
         <is>
-          <t>conditional</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AG374" t="inlineStr">
@@ -69855,12 +69860,12 @@
       </c>
       <c r="AJ374" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK374" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 172.</t>
+          <t>Australia NINDSS rubella notifications excluding the separately reported congenital category.</t>
         </is>
       </c>
       <c r="AM374" t="inlineStr">
@@ -69873,75 +69878,70 @@
       </c>
       <c r="AO374" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP374" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ374" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR374" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS374" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_172</t>
+          <t>SER_AU_RUBELLA</t>
         </is>
       </c>
       <c r="AT374" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU374" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV374" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW374" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX374" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY374" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ374" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA374" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB374" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC374" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -69973,118 +69973,521 @@
       </c>
       <c r="F375" t="inlineStr">
         <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>D040</t>
+        </is>
+      </c>
+      <c r="I375" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="J375" t="inlineStr">
+        <is>
+          <t>风疹</t>
+        </is>
+      </c>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L375" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M375" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N375" t="n">
+        <v>0</v>
+      </c>
+      <c r="O375" t="n">
+        <v>0</v>
+      </c>
+      <c r="R375" t="n">
+        <v>0</v>
+      </c>
+      <c r="S375" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U375" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_172</t>
+        </is>
+      </c>
+      <c r="AA375" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO375" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP375" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ375" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR375" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS375" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_172</t>
+        </is>
+      </c>
+      <c r="AT375" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU375" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV375" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW375" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX375" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY375" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ375" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA375" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB375" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC375" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>D040</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>rubella</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>D040</t>
+        </is>
+      </c>
+      <c r="I376" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="J376" t="inlineStr">
+        <is>
+          <t>风疹</t>
+        </is>
+      </c>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L376" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M376" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N376" t="n">
+        <v>0</v>
+      </c>
+      <c r="O376" t="n">
+        <v>0</v>
+      </c>
+      <c r="U376" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_172</t>
+        </is>
+      </c>
+      <c r="V376" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_172</t>
+        </is>
+      </c>
+      <c r="W376" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X376" t="inlineStr">
+        <is>
+          <t>German measles</t>
+        </is>
+      </c>
+      <c r="Y376" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z376" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA376" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB376" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC376" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD376" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE376" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF376" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG376" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH376" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI376" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ376" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK376" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 172.</t>
+        </is>
+      </c>
+      <c r="AM376" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN376" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO376" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP376" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ376" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR376" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS376" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_172</t>
+        </is>
+      </c>
+      <c r="AT376" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU376" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV376" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW376" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX376" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY376" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ376" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA376" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB376" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC376" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>D040</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>rubella</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="G375" t="inlineStr">
+      <c r="G377" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="H375" t="inlineStr">
-        <is>
-          <t>D040</t>
-        </is>
-      </c>
-      <c r="I375" t="inlineStr">
-        <is>
-          <t>Rubella</t>
-        </is>
-      </c>
-      <c r="J375" t="inlineStr">
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>D040</t>
+        </is>
+      </c>
+      <c r="I377" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="J377" t="inlineStr">
         <is>
           <t>风疹</t>
         </is>
       </c>
-      <c r="K375" t="inlineStr">
+      <c r="K377" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L375" t="inlineStr">
+      <c r="L377" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="M375" t="inlineStr">
+      <c r="M377" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N375" t="n">
-        <v>0</v>
-      </c>
-      <c r="O375" t="n">
-        <v>0</v>
-      </c>
-      <c r="R375" t="n">
-        <v>0</v>
-      </c>
-      <c r="S375" t="inlineStr">
+      <c r="N377" t="n">
+        <v>0</v>
+      </c>
+      <c r="O377" t="n">
+        <v>0</v>
+      </c>
+      <c r="R377" t="n">
+        <v>0</v>
+      </c>
+      <c r="S377" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO375" t="inlineStr">
+      <c r="AO377" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP375" t="inlineStr">
+      <c r="AP377" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR375" t="inlineStr">
+      <c r="AR377" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS375" t="inlineStr"/>
-      <c r="AT375" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU375" t="inlineStr">
+      <c r="AS377" t="inlineStr"/>
+      <c r="AT377" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU377" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV375" t="inlineStr">
+      <c r="AV377" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW375" t="inlineStr">
+      <c r="AW377" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX375" t="inlineStr">
+      <c r="AX377" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY375" t="inlineStr">
+      <c r="AY377" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ375" t="inlineStr">
+      <c r="AZ377" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA375" t="inlineStr">
+      <c r="BA377" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB375" t="inlineStr">
+      <c r="BB377" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC375" t="inlineStr">
+      <c r="BC377" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -70206,7 +70609,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="10">
@@ -70216,7 +70619,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="11">
@@ -70236,7 +70639,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d040/2026-2029.xlsx
+++ b/diseases/d040/2026-2029.xlsx
@@ -69580,12 +69580,12 @@
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H373" t="inlineStr">
@@ -69610,22 +69610,25 @@
       </c>
       <c r="L373" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N373" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O373" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P373" t="n">
+        <v>1</v>
       </c>
       <c r="R373" t="n">
-        <v>0</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S373" t="inlineStr">
         <is>
@@ -69634,17 +69637,17 @@
       </c>
       <c r="U373" t="inlineStr">
         <is>
-          <t>SER_AU_RUBELLA</t>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
         </is>
       </c>
       <c r="AA373" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO373" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP373" t="inlineStr">
@@ -69654,12 +69657,12 @@
       </c>
       <c r="AQ373" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS373" t="inlineStr">
         <is>
-          <t>SER_AU_RUBELLA</t>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
         </is>
       </c>
       <c r="AT373" t="n">
@@ -69667,47 +69670,47 @@
       </c>
       <c r="AU373" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV373" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW373" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX373" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY373" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ373" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA373" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB373" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC373" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -69739,12 +69742,12 @@
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
@@ -69769,33 +69772,36 @@
       </c>
       <c r="L374" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N374" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O374" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P374" t="n">
+        <v>1</v>
       </c>
       <c r="U374" t="inlineStr">
         <is>
-          <t>SER_AU_RUBELLA</t>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
         </is>
       </c>
       <c r="V374" t="inlineStr">
         <is>
-          <t>SER_AU_RUBELLA</t>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
         </is>
       </c>
       <c r="W374" t="inlineStr">
         <is>
-          <t>SRC_AU_NINDSS</t>
+          <t>SRC_JP_NIID</t>
         </is>
       </c>
       <c r="X374" t="inlineStr">
@@ -69815,7 +69821,7 @@
       </c>
       <c r="AA374" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AB374" t="inlineStr">
@@ -69825,7 +69831,7 @@
       </c>
       <c r="AC374" t="inlineStr">
         <is>
-          <t>country:AU:national</t>
+          <t>country:JP:national</t>
         </is>
       </c>
       <c r="AD374" t="inlineStr">
@@ -69865,7 +69871,7 @@
       </c>
       <c r="AK374" t="inlineStr">
         <is>
-          <t>Australia NINDSS rubella notifications excluding the separately reported congenital category.</t>
+          <t>Japan NIID rubella notifications, excluding congenital rubella syndrome.</t>
         </is>
       </c>
       <c r="AM374" t="inlineStr">
@@ -69878,7 +69884,7 @@
       </c>
       <c r="AO374" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP374" t="inlineStr">
@@ -69888,12 +69894,12 @@
       </c>
       <c r="AQ374" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS374" t="inlineStr">
         <is>
-          <t>SER_AU_RUBELLA</t>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
         </is>
       </c>
       <c r="AT374" t="n">
@@ -69901,47 +69907,47 @@
       </c>
       <c r="AU374" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV374" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW374" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX374" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY374" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ374" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA374" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB374" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC374" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -69973,12 +69979,12 @@
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H375" t="inlineStr">
@@ -70027,7 +70033,7 @@
       </c>
       <c r="U375" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_172</t>
+          <t>SER_AU_RUBELLA</t>
         </is>
       </c>
       <c r="AA375" t="inlineStr">
@@ -70037,75 +70043,70 @@
       </c>
       <c r="AO375" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP375" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ375" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR375" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS375" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_172</t>
+          <t>SER_AU_RUBELLA</t>
         </is>
       </c>
       <c r="AT375" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU375" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV375" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW375" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX375" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY375" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ375" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA375" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB375" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC375" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -70137,12 +70138,12 @@
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H376" t="inlineStr">
@@ -70183,22 +70184,22 @@
       </c>
       <c r="U376" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_172</t>
+          <t>SER_AU_RUBELLA</t>
         </is>
       </c>
       <c r="V376" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_172</t>
+          <t>SER_AU_RUBELLA</t>
         </is>
       </c>
       <c r="W376" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_AU_NINDSS</t>
         </is>
       </c>
       <c r="X376" t="inlineStr">
         <is>
-          <t>German measles</t>
+          <t>Rubella</t>
         </is>
       </c>
       <c r="Y376" t="inlineStr">
@@ -70208,7 +70209,7 @@
       </c>
       <c r="Z376" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA376" t="inlineStr">
@@ -70223,7 +70224,7 @@
       </c>
       <c r="AC376" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:AU:national</t>
         </is>
       </c>
       <c r="AD376" t="inlineStr">
@@ -70238,7 +70239,7 @@
       </c>
       <c r="AF376" t="inlineStr">
         <is>
-          <t>conditional</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AG376" t="inlineStr">
@@ -70258,12 +70259,12 @@
       </c>
       <c r="AJ376" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK376" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 172.</t>
+          <t>Australia NINDSS rubella notifications excluding the separately reported congenital category.</t>
         </is>
       </c>
       <c r="AM376" t="inlineStr">
@@ -70276,75 +70277,70 @@
       </c>
       <c r="AO376" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP376" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ376" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR376" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS376" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_172</t>
+          <t>SER_AU_RUBELLA</t>
         </is>
       </c>
       <c r="AT376" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU376" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV376" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW376" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX376" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY376" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ376" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA376" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB376" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC376" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -70376,118 +70372,521 @@
       </c>
       <c r="F377" t="inlineStr">
         <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>D040</t>
+        </is>
+      </c>
+      <c r="I377" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="J377" t="inlineStr">
+        <is>
+          <t>风疹</t>
+        </is>
+      </c>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L377" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M377" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N377" t="n">
+        <v>0</v>
+      </c>
+      <c r="O377" t="n">
+        <v>0</v>
+      </c>
+      <c r="R377" t="n">
+        <v>0</v>
+      </c>
+      <c r="S377" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U377" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_172</t>
+        </is>
+      </c>
+      <c r="AA377" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO377" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP377" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ377" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR377" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS377" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_172</t>
+        </is>
+      </c>
+      <c r="AT377" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU377" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV377" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW377" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX377" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY377" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ377" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA377" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB377" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC377" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>D040</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>rubella</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>D040</t>
+        </is>
+      </c>
+      <c r="I378" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="J378" t="inlineStr">
+        <is>
+          <t>风疹</t>
+        </is>
+      </c>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L378" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M378" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N378" t="n">
+        <v>0</v>
+      </c>
+      <c r="O378" t="n">
+        <v>0</v>
+      </c>
+      <c r="U378" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_172</t>
+        </is>
+      </c>
+      <c r="V378" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_172</t>
+        </is>
+      </c>
+      <c r="W378" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X378" t="inlineStr">
+        <is>
+          <t>German measles</t>
+        </is>
+      </c>
+      <c r="Y378" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z378" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA378" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB378" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC378" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD378" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE378" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF378" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG378" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH378" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI378" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ378" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK378" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 172.</t>
+        </is>
+      </c>
+      <c r="AM378" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN378" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO378" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP378" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ378" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR378" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS378" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_172</t>
+        </is>
+      </c>
+      <c r="AT378" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU378" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV378" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW378" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX378" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY378" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ378" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA378" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB378" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC378" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>D040</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>rubella</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="G377" t="inlineStr">
+      <c r="G379" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="H377" t="inlineStr">
-        <is>
-          <t>D040</t>
-        </is>
-      </c>
-      <c r="I377" t="inlineStr">
-        <is>
-          <t>Rubella</t>
-        </is>
-      </c>
-      <c r="J377" t="inlineStr">
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>D040</t>
+        </is>
+      </c>
+      <c r="I379" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="J379" t="inlineStr">
         <is>
           <t>风疹</t>
         </is>
       </c>
-      <c r="K377" t="inlineStr">
+      <c r="K379" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L377" t="inlineStr">
+      <c r="L379" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="M377" t="inlineStr">
+      <c r="M379" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N377" t="n">
-        <v>0</v>
-      </c>
-      <c r="O377" t="n">
-        <v>0</v>
-      </c>
-      <c r="R377" t="n">
-        <v>0</v>
-      </c>
-      <c r="S377" t="inlineStr">
+      <c r="N379" t="n">
+        <v>0</v>
+      </c>
+      <c r="O379" t="n">
+        <v>0</v>
+      </c>
+      <c r="R379" t="n">
+        <v>0</v>
+      </c>
+      <c r="S379" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO377" t="inlineStr">
+      <c r="AO379" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP377" t="inlineStr">
+      <c r="AP379" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR377" t="inlineStr">
+      <c r="AR379" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS377" t="inlineStr"/>
-      <c r="AT377" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU377" t="inlineStr">
+      <c r="AS379" t="inlineStr"/>
+      <c r="AT379" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU379" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV377" t="inlineStr">
+      <c r="AV379" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW377" t="inlineStr">
+      <c r="AW379" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX377" t="inlineStr">
+      <c r="AX379" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY377" t="inlineStr">
+      <c r="AY379" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ377" t="inlineStr">
+      <c r="AZ379" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA377" t="inlineStr">
+      <c r="BA379" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB377" t="inlineStr">
+      <c r="BB379" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC377" t="inlineStr">
+      <c r="BC379" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -70609,7 +71008,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="10">
@@ -70619,7 +71018,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="11">
@@ -70639,7 +71038,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="13">
@@ -70671,7 +71070,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d040/2026-2029.xlsx
+++ b/diseases/d040/2026-2029.xlsx
@@ -45292,7 +45292,7 @@
       </c>
       <c r="AM239" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN239" t="b">
@@ -54897,7 +54897,7 @@
       </c>
       <c r="AM292" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN292" t="b">
@@ -64109,13 +64109,13 @@
         </is>
       </c>
       <c r="N343" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O343" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R343" t="n">
-        <v>0</v>
+        <v>0.00367281181951979</v>
       </c>
       <c r="S343" t="inlineStr">
         <is>
@@ -64268,10 +64268,10 @@
         </is>
       </c>
       <c r="N344" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O344" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U344" t="inlineStr">
         <is>
@@ -64360,7 +64360,7 @@
       </c>
       <c r="AM344" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN344" t="b">
@@ -65457,12 +65457,12 @@
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
@@ -65496,100 +65496,84 @@
         </is>
       </c>
       <c r="N352" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="O352" t="n">
+        <v>43</v>
+      </c>
+      <c r="Q352" t="n">
         <v>0</v>
       </c>
       <c r="R352" t="n">
-        <v>0</v>
+        <v>0.003043355597483661</v>
       </c>
       <c r="S352" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U352" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_172</t>
-        </is>
-      </c>
-      <c r="AA352" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO352" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP352" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ352" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR352" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS352" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_172</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS352" t="inlineStr"/>
       <c r="AT352" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU352" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV352" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW352" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX352" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY352" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ352" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA352" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB352" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC352" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -65616,7 +65600,7 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
@@ -65665,98 +65649,23 @@
       <c r="O353" t="n">
         <v>0</v>
       </c>
+      <c r="R353" t="n">
+        <v>0</v>
+      </c>
+      <c r="S353" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U353" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_172</t>
         </is>
       </c>
-      <c r="V353" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_172</t>
-        </is>
-      </c>
-      <c r="W353" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X353" t="inlineStr">
-        <is>
-          <t>German measles</t>
-        </is>
-      </c>
-      <c r="Y353" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z353" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA353" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB353" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC353" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD353" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE353" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF353" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG353" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH353" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI353" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ353" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK353" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 172.</t>
-        </is>
-      </c>
-      <c r="AM353" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN353" t="b">
-        <v>1</v>
       </c>
       <c r="AO353" t="inlineStr">
         <is>
@@ -65855,17 +65764,17 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
@@ -65904,76 +65813,170 @@
       <c r="O354" t="n">
         <v>0</v>
       </c>
-      <c r="R354" t="n">
-        <v>0</v>
-      </c>
-      <c r="S354" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U354" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_172</t>
+        </is>
+      </c>
+      <c r="V354" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_172</t>
+        </is>
+      </c>
+      <c r="W354" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X354" t="inlineStr">
+        <is>
+          <t>German measles</t>
+        </is>
+      </c>
+      <c r="Y354" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z354" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA354" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB354" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC354" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD354" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE354" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF354" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG354" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH354" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI354" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ354" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK354" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 172.</t>
+        </is>
+      </c>
+      <c r="AM354" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN354" t="b">
+        <v>1</v>
       </c>
       <c r="AO354" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP354" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ354" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR354" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS354" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS354" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_172</t>
+        </is>
+      </c>
       <c r="AT354" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU354" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV354" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW354" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX354" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY354" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ354" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA354" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB354" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC354" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -66005,12 +66008,12 @@
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
@@ -66057,87 +66060,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U355" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_RUBELLA</t>
-        </is>
-      </c>
-      <c r="AA355" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO355" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP355" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ355" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR355" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS355" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_RUBELLA</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS355" t="inlineStr"/>
       <c r="AT355" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU355" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV355" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW355" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX355" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY355" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ355" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA355" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB355" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC355" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -66164,7 +66148,7 @@
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
@@ -66213,98 +66197,23 @@
       <c r="O356" t="n">
         <v>0</v>
       </c>
+      <c r="R356" t="n">
+        <v>0</v>
+      </c>
+      <c r="S356" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U356" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_RUBELLA</t>
         </is>
       </c>
-      <c r="V356" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_RUBELLA</t>
-        </is>
-      </c>
-      <c r="W356" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X356" t="inlineStr">
-        <is>
-          <t>Röda hund</t>
-        </is>
-      </c>
-      <c r="Y356" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z356" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA356" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB356" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC356" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD356" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE356" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF356" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG356" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH356" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI356" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ356" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK356" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; Excludes congenital rubella syndrome unless source definition changes.</t>
-        </is>
-      </c>
-      <c r="AM356" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN356" t="b">
-        <v>1</v>
       </c>
       <c r="AO356" t="inlineStr">
         <is>
@@ -66403,17 +66312,17 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
@@ -66438,7 +66347,7 @@
       </c>
       <c r="L357" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M357" t="inlineStr">
@@ -66452,26 +66361,98 @@
       <c r="O357" t="n">
         <v>0</v>
       </c>
-      <c r="P357" t="n">
-        <v>0</v>
-      </c>
-      <c r="R357" t="n">
-        <v>0</v>
-      </c>
-      <c r="S357" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U357" t="inlineStr">
         <is>
-          <t>SER_JP_RUBELLA_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_RUBELLA</t>
+        </is>
+      </c>
+      <c r="V357" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_RUBELLA</t>
+        </is>
+      </c>
+      <c r="W357" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X357" t="inlineStr">
+        <is>
+          <t>Röda hund</t>
+        </is>
+      </c>
+      <c r="Y357" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z357" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA357" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB357" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC357" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD357" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE357" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF357" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG357" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH357" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI357" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ357" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK357" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; Excludes congenital rubella syndrome unless source definition changes.</t>
+        </is>
+      </c>
+      <c r="AM357" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN357" t="b">
+        <v>1</v>
       </c>
       <c r="AO357" t="inlineStr">
         <is>
@@ -66480,7 +66461,7 @@
       </c>
       <c r="AP357" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ357" t="inlineStr">
@@ -66488,57 +66469,62 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR357" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS357" t="inlineStr">
         <is>
-          <t>SER_JP_RUBELLA_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_RUBELLA</t>
         </is>
       </c>
       <c r="AT357" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU357" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV357" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW357" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX357" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY357" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ357" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA357" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB357" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC357" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -66565,7 +66551,7 @@
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
@@ -66617,98 +66603,23 @@
       <c r="P358" t="n">
         <v>0</v>
       </c>
+      <c r="R358" t="n">
+        <v>0</v>
+      </c>
+      <c r="S358" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U358" t="inlineStr">
         <is>
           <t>SER_JP_RUBELLA_WEEKLY</t>
         </is>
       </c>
-      <c r="V358" t="inlineStr">
-        <is>
-          <t>SER_JP_RUBELLA_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W358" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X358" t="inlineStr">
-        <is>
-          <t>Rubella</t>
-        </is>
-      </c>
-      <c r="Y358" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z358" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA358" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB358" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC358" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD358" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE358" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF358" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG358" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH358" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI358" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ358" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK358" t="inlineStr">
-        <is>
-          <t>Japan NIID rubella notifications, excluding congenital rubella syndrome.</t>
-        </is>
-      </c>
-      <c r="AM358" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN358" t="b">
-        <v>1</v>
       </c>
       <c r="AO358" t="inlineStr">
         <is>
@@ -66802,17 +66713,17 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
@@ -66854,12 +66765,34 @@
       <c r="P359" t="n">
         <v>0</v>
       </c>
-      <c r="R359" t="n">
-        <v>0</v>
-      </c>
-      <c r="S359" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U359" t="inlineStr">
+        <is>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V359" t="inlineStr">
+        <is>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W359" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X359" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="Y359" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z359" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA359" t="inlineStr">
@@ -66867,6 +66800,64 @@
           <t>weekly</t>
         </is>
       </c>
+      <c r="AB359" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC359" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD359" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE359" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF359" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG359" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH359" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI359" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ359" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK359" t="inlineStr">
+        <is>
+          <t>Japan NIID rubella notifications, excluding congenital rubella syndrome.</t>
+        </is>
+      </c>
+      <c r="AM359" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN359" t="b">
+        <v>1</v>
+      </c>
       <c r="AO359" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -66874,7 +66865,7 @@
       </c>
       <c r="AP359" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ359" t="inlineStr">
@@ -66884,55 +66875,55 @@
       </c>
       <c r="AS359" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_RUBELLA; SER_SG_HIST_RUBELLA</t>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
         </is>
       </c>
       <c r="AT359" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU359" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV359" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW359" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX359" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY359" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ359" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA359" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB359" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC359" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -66959,7 +66950,7 @@
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
@@ -67011,98 +67002,18 @@
       <c r="P360" t="n">
         <v>0</v>
       </c>
-      <c r="U360" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_RUBELLA</t>
-        </is>
-      </c>
-      <c r="V360" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_RUBELLA</t>
-        </is>
-      </c>
-      <c r="W360" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X360" t="inlineStr">
-        <is>
-          <t>Rubella</t>
-        </is>
-      </c>
-      <c r="Y360" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z360" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R360" t="n">
+        <v>0</v>
+      </c>
+      <c r="S360" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA360" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB360" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC360" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD360" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE360" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF360" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG360" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH360" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI360" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ360" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK360" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM360" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN360" t="b">
-        <v>1</v>
       </c>
       <c r="AO360" t="inlineStr">
         <is>
@@ -67196,17 +67107,17 @@
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H361" t="inlineStr">
@@ -67231,7 +67142,7 @@
       </c>
       <c r="L361" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M361" t="inlineStr">
@@ -67248,17 +67159,34 @@
       <c r="P361" t="n">
         <v>0</v>
       </c>
-      <c r="R361" t="n">
-        <v>0</v>
-      </c>
-      <c r="S361" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U361" t="inlineStr">
         <is>
-          <t>SER_JP_RUBELLA_WEEKLY</t>
+          <t>SER_SG_CDA_RUBELLA</t>
+        </is>
+      </c>
+      <c r="V361" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_RUBELLA</t>
+        </is>
+      </c>
+      <c r="W361" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X361" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="Y361" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z361" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA361" t="inlineStr">
@@ -67266,6 +67194,64 @@
           <t>weekly</t>
         </is>
       </c>
+      <c r="AB361" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC361" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD361" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE361" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF361" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG361" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH361" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI361" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ361" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK361" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM361" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN361" t="b">
+        <v>1</v>
+      </c>
       <c r="AO361" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -67273,7 +67259,7 @@
       </c>
       <c r="AP361" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ361" t="inlineStr">
@@ -67283,55 +67269,55 @@
       </c>
       <c r="AS361" t="inlineStr">
         <is>
-          <t>SER_JP_RUBELLA_WEEKLY</t>
+          <t>SER_SG_CDA_RUBELLA; SER_SG_HIST_RUBELLA</t>
         </is>
       </c>
       <c r="AT361" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU361" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV361" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW361" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX361" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY361" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ361" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA361" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB361" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC361" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -67358,7 +67344,7 @@
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
@@ -67410,98 +67396,23 @@
       <c r="P362" t="n">
         <v>0</v>
       </c>
+      <c r="R362" t="n">
+        <v>0</v>
+      </c>
+      <c r="S362" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U362" t="inlineStr">
         <is>
           <t>SER_JP_RUBELLA_WEEKLY</t>
         </is>
       </c>
-      <c r="V362" t="inlineStr">
-        <is>
-          <t>SER_JP_RUBELLA_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W362" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X362" t="inlineStr">
-        <is>
-          <t>Rubella</t>
-        </is>
-      </c>
-      <c r="Y362" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z362" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA362" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB362" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC362" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD362" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE362" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF362" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG362" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH362" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI362" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ362" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK362" t="inlineStr">
-        <is>
-          <t>Japan NIID rubella notifications, excluding congenital rubella syndrome.</t>
-        </is>
-      </c>
-      <c r="AM362" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN362" t="b">
-        <v>1</v>
       </c>
       <c r="AO362" t="inlineStr">
         <is>
@@ -67595,17 +67506,17 @@
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
@@ -67647,12 +67558,34 @@
       <c r="P363" t="n">
         <v>0</v>
       </c>
-      <c r="R363" t="n">
-        <v>0</v>
-      </c>
-      <c r="S363" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U363" t="inlineStr">
+        <is>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V363" t="inlineStr">
+        <is>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W363" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X363" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="Y363" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z363" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA363" t="inlineStr">
@@ -67660,6 +67593,64 @@
           <t>weekly</t>
         </is>
       </c>
+      <c r="AB363" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC363" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD363" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE363" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF363" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG363" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH363" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI363" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ363" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK363" t="inlineStr">
+        <is>
+          <t>Japan NIID rubella notifications, excluding congenital rubella syndrome.</t>
+        </is>
+      </c>
+      <c r="AM363" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN363" t="b">
+        <v>1</v>
+      </c>
       <c r="AO363" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -67667,7 +67658,7 @@
       </c>
       <c r="AP363" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ363" t="inlineStr">
@@ -67677,55 +67668,55 @@
       </c>
       <c r="AS363" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_RUBELLA; SER_SG_HIST_RUBELLA</t>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
         </is>
       </c>
       <c r="AT363" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU363" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV363" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW363" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX363" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY363" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ363" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA363" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB363" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC363" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -67752,7 +67743,7 @@
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
@@ -67804,98 +67795,18 @@
       <c r="P364" t="n">
         <v>0</v>
       </c>
-      <c r="U364" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_RUBELLA</t>
-        </is>
-      </c>
-      <c r="V364" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_RUBELLA</t>
-        </is>
-      </c>
-      <c r="W364" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X364" t="inlineStr">
-        <is>
-          <t>Rubella</t>
-        </is>
-      </c>
-      <c r="Y364" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z364" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R364" t="n">
+        <v>0</v>
+      </c>
+      <c r="S364" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA364" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB364" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC364" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD364" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE364" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF364" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG364" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH364" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI364" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ364" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK364" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM364" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN364" t="b">
-        <v>1</v>
       </c>
       <c r="AO364" t="inlineStr">
         <is>
@@ -67989,17 +67900,17 @@
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H365" t="inlineStr">
@@ -68024,7 +67935,7 @@
       </c>
       <c r="L365" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M365" t="inlineStr">
@@ -68041,17 +67952,34 @@
       <c r="P365" t="n">
         <v>0</v>
       </c>
-      <c r="R365" t="n">
-        <v>0</v>
-      </c>
-      <c r="S365" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U365" t="inlineStr">
         <is>
-          <t>SER_JP_RUBELLA_WEEKLY</t>
+          <t>SER_SG_CDA_RUBELLA</t>
+        </is>
+      </c>
+      <c r="V365" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_RUBELLA</t>
+        </is>
+      </c>
+      <c r="W365" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X365" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="Y365" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z365" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA365" t="inlineStr">
@@ -68059,6 +67987,64 @@
           <t>weekly</t>
         </is>
       </c>
+      <c r="AB365" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC365" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD365" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE365" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF365" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG365" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH365" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI365" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ365" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK365" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM365" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN365" t="b">
+        <v>1</v>
+      </c>
       <c r="AO365" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -68066,7 +68052,7 @@
       </c>
       <c r="AP365" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ365" t="inlineStr">
@@ -68076,55 +68062,55 @@
       </c>
       <c r="AS365" t="inlineStr">
         <is>
-          <t>SER_JP_RUBELLA_WEEKLY</t>
+          <t>SER_SG_CDA_RUBELLA; SER_SG_HIST_RUBELLA</t>
         </is>
       </c>
       <c r="AT365" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU365" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV365" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW365" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX365" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY365" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ365" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA365" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB365" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC365" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -68151,7 +68137,7 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
@@ -68203,98 +68189,23 @@
       <c r="P366" t="n">
         <v>0</v>
       </c>
+      <c r="R366" t="n">
+        <v>0</v>
+      </c>
+      <c r="S366" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U366" t="inlineStr">
         <is>
           <t>SER_JP_RUBELLA_WEEKLY</t>
         </is>
       </c>
-      <c r="V366" t="inlineStr">
-        <is>
-          <t>SER_JP_RUBELLA_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W366" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X366" t="inlineStr">
-        <is>
-          <t>Rubella</t>
-        </is>
-      </c>
-      <c r="Y366" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z366" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA366" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB366" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC366" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD366" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE366" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF366" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG366" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH366" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI366" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ366" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK366" t="inlineStr">
-        <is>
-          <t>Japan NIID rubella notifications, excluding congenital rubella syndrome.</t>
-        </is>
-      </c>
-      <c r="AM366" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN366" t="b">
-        <v>1</v>
       </c>
       <c r="AO366" t="inlineStr">
         <is>
@@ -68388,17 +68299,17 @@
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H367" t="inlineStr">
@@ -68440,12 +68351,34 @@
       <c r="P367" t="n">
         <v>0</v>
       </c>
-      <c r="R367" t="n">
-        <v>0</v>
-      </c>
-      <c r="S367" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U367" t="inlineStr">
+        <is>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V367" t="inlineStr">
+        <is>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W367" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X367" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="Y367" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z367" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA367" t="inlineStr">
@@ -68453,6 +68386,64 @@
           <t>weekly</t>
         </is>
       </c>
+      <c r="AB367" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC367" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD367" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE367" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF367" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG367" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH367" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI367" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ367" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK367" t="inlineStr">
+        <is>
+          <t>Japan NIID rubella notifications, excluding congenital rubella syndrome.</t>
+        </is>
+      </c>
+      <c r="AM367" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN367" t="b">
+        <v>1</v>
+      </c>
       <c r="AO367" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -68460,7 +68451,7 @@
       </c>
       <c r="AP367" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ367" t="inlineStr">
@@ -68470,55 +68461,55 @@
       </c>
       <c r="AS367" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_RUBELLA; SER_SG_HIST_RUBELLA</t>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
         </is>
       </c>
       <c r="AT367" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU367" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV367" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW367" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX367" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY367" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ367" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA367" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB367" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC367" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -68545,7 +68536,7 @@
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
@@ -68597,98 +68588,18 @@
       <c r="P368" t="n">
         <v>0</v>
       </c>
-      <c r="U368" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_RUBELLA</t>
-        </is>
-      </c>
-      <c r="V368" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_RUBELLA</t>
-        </is>
-      </c>
-      <c r="W368" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X368" t="inlineStr">
-        <is>
-          <t>Rubella</t>
-        </is>
-      </c>
-      <c r="Y368" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z368" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R368" t="n">
+        <v>0</v>
+      </c>
+      <c r="S368" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA368" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB368" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC368" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD368" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE368" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF368" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG368" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH368" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI368" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ368" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK368" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM368" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN368" t="b">
-        <v>1</v>
       </c>
       <c r="AO368" t="inlineStr">
         <is>
@@ -68782,17 +68693,17 @@
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H369" t="inlineStr">
@@ -68817,7 +68728,7 @@
       </c>
       <c r="L369" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M369" t="inlineStr">
@@ -68834,17 +68745,34 @@
       <c r="P369" t="n">
         <v>0</v>
       </c>
-      <c r="R369" t="n">
-        <v>0</v>
-      </c>
-      <c r="S369" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U369" t="inlineStr">
         <is>
-          <t>SER_JP_RUBELLA_WEEKLY</t>
+          <t>SER_SG_CDA_RUBELLA</t>
+        </is>
+      </c>
+      <c r="V369" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_RUBELLA</t>
+        </is>
+      </c>
+      <c r="W369" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X369" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="Y369" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z369" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA369" t="inlineStr">
@@ -68852,6 +68780,64 @@
           <t>weekly</t>
         </is>
       </c>
+      <c r="AB369" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC369" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD369" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE369" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF369" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG369" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH369" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI369" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ369" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK369" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM369" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN369" t="b">
+        <v>1</v>
+      </c>
       <c r="AO369" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -68859,7 +68845,7 @@
       </c>
       <c r="AP369" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ369" t="inlineStr">
@@ -68869,55 +68855,55 @@
       </c>
       <c r="AS369" t="inlineStr">
         <is>
-          <t>SER_JP_RUBELLA_WEEKLY</t>
+          <t>SER_SG_CDA_RUBELLA; SER_SG_HIST_RUBELLA</t>
         </is>
       </c>
       <c r="AT369" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU369" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV369" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW369" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX369" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY369" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ369" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA369" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB369" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC369" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -68944,7 +68930,7 @@
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
@@ -68996,98 +68982,23 @@
       <c r="P370" t="n">
         <v>0</v>
       </c>
+      <c r="R370" t="n">
+        <v>0</v>
+      </c>
+      <c r="S370" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U370" t="inlineStr">
         <is>
           <t>SER_JP_RUBELLA_WEEKLY</t>
         </is>
       </c>
-      <c r="V370" t="inlineStr">
-        <is>
-          <t>SER_JP_RUBELLA_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W370" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X370" t="inlineStr">
-        <is>
-          <t>Rubella</t>
-        </is>
-      </c>
-      <c r="Y370" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z370" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA370" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB370" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC370" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD370" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE370" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF370" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG370" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH370" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI370" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ370" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK370" t="inlineStr">
-        <is>
-          <t>Japan NIID rubella notifications, excluding congenital rubella syndrome.</t>
-        </is>
-      </c>
-      <c r="AM370" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN370" t="b">
-        <v>1</v>
       </c>
       <c r="AO370" t="inlineStr">
         <is>
@@ -69181,17 +69092,17 @@
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H371" t="inlineStr">
@@ -69233,12 +69144,34 @@
       <c r="P371" t="n">
         <v>0</v>
       </c>
-      <c r="R371" t="n">
-        <v>0</v>
-      </c>
-      <c r="S371" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U371" t="inlineStr">
+        <is>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V371" t="inlineStr">
+        <is>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W371" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X371" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="Y371" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z371" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA371" t="inlineStr">
@@ -69246,6 +69179,64 @@
           <t>weekly</t>
         </is>
       </c>
+      <c r="AB371" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC371" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD371" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE371" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF371" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG371" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH371" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI371" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ371" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK371" t="inlineStr">
+        <is>
+          <t>Japan NIID rubella notifications, excluding congenital rubella syndrome.</t>
+        </is>
+      </c>
+      <c r="AM371" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN371" t="b">
+        <v>1</v>
+      </c>
       <c r="AO371" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -69253,7 +69244,7 @@
       </c>
       <c r="AP371" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ371" t="inlineStr">
@@ -69263,55 +69254,55 @@
       </c>
       <c r="AS371" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_RUBELLA; SER_SG_HIST_RUBELLA</t>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
         </is>
       </c>
       <c r="AT371" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU371" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV371" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW371" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX371" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY371" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ371" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA371" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB371" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC371" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -69338,7 +69329,7 @@
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
@@ -69390,98 +69381,18 @@
       <c r="P372" t="n">
         <v>0</v>
       </c>
-      <c r="U372" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_RUBELLA</t>
-        </is>
-      </c>
-      <c r="V372" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_RUBELLA</t>
-        </is>
-      </c>
-      <c r="W372" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X372" t="inlineStr">
-        <is>
-          <t>Rubella</t>
-        </is>
-      </c>
-      <c r="Y372" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z372" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R372" t="n">
+        <v>0</v>
+      </c>
+      <c r="S372" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA372" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB372" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC372" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD372" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE372" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF372" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG372" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH372" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI372" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ372" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK372" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM372" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN372" t="b">
-        <v>1</v>
       </c>
       <c r="AO372" t="inlineStr">
         <is>
@@ -69575,17 +69486,17 @@
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H373" t="inlineStr">
@@ -69610,7 +69521,7 @@
       </c>
       <c r="L373" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M373" t="inlineStr">
@@ -69619,32 +69530,107 @@
         </is>
       </c>
       <c r="N373" t="n">
+        <v>0</v>
+      </c>
+      <c r="O373" t="n">
+        <v>0</v>
+      </c>
+      <c r="P373" t="n">
+        <v>0</v>
+      </c>
+      <c r="U373" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_RUBELLA</t>
+        </is>
+      </c>
+      <c r="V373" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_RUBELLA</t>
+        </is>
+      </c>
+      <c r="W373" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X373" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="Y373" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z373" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA373" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB373" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC373" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD373" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE373" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF373" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG373" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH373" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI373" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ373" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK373" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM373" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN373" t="b">
         <v>1</v>
       </c>
-      <c r="O373" t="n">
-        <v>1</v>
-      </c>
-      <c r="P373" t="n">
-        <v>1</v>
-      </c>
-      <c r="R373" t="n">
-        <v>0.0008168084075657662</v>
-      </c>
-      <c r="S373" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U373" t="inlineStr">
-        <is>
-          <t>SER_JP_RUBELLA_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA373" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO373" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -69652,7 +69638,7 @@
       </c>
       <c r="AP373" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ373" t="inlineStr">
@@ -69662,55 +69648,55 @@
       </c>
       <c r="AS373" t="inlineStr">
         <is>
-          <t>SER_JP_RUBELLA_WEEKLY</t>
+          <t>SER_SG_CDA_RUBELLA; SER_SG_HIST_RUBELLA</t>
         </is>
       </c>
       <c r="AT373" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU373" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV373" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW373" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX373" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY373" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ373" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA373" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB373" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC373" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -69737,7 +69723,7 @@
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
@@ -69789,98 +69775,23 @@
       <c r="P374" t="n">
         <v>1</v>
       </c>
+      <c r="R374" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S374" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U374" t="inlineStr">
         <is>
           <t>SER_JP_RUBELLA_WEEKLY</t>
         </is>
       </c>
-      <c r="V374" t="inlineStr">
-        <is>
-          <t>SER_JP_RUBELLA_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W374" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X374" t="inlineStr">
-        <is>
-          <t>Rubella</t>
-        </is>
-      </c>
-      <c r="Y374" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z374" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA374" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB374" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC374" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD374" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE374" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF374" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG374" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH374" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI374" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ374" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK374" t="inlineStr">
-        <is>
-          <t>Japan NIID rubella notifications, excluding congenital rubella syndrome.</t>
-        </is>
-      </c>
-      <c r="AM374" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN374" t="b">
-        <v>1</v>
       </c>
       <c r="AO374" t="inlineStr">
         <is>
@@ -69974,17 +69885,17 @@
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H375" t="inlineStr">
@@ -70009,41 +69920,119 @@
       </c>
       <c r="L375" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N375" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O375" t="n">
-        <v>0</v>
-      </c>
-      <c r="R375" t="n">
-        <v>0</v>
-      </c>
-      <c r="S375" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="P375" t="n">
+        <v>1</v>
       </c>
       <c r="U375" t="inlineStr">
         <is>
-          <t>SER_AU_RUBELLA</t>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V375" t="inlineStr">
+        <is>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W375" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X375" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="Y375" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z375" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA375" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB375" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC375" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD375" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE375" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF375" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG375" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH375" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI375" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ375" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK375" t="inlineStr">
+        <is>
+          <t>Japan NIID rubella notifications, excluding congenital rubella syndrome.</t>
+        </is>
+      </c>
+      <c r="AM375" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN375" t="b">
+        <v>1</v>
       </c>
       <c r="AO375" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP375" t="inlineStr">
@@ -70053,12 +70042,12 @@
       </c>
       <c r="AQ375" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS375" t="inlineStr">
         <is>
-          <t>SER_AU_RUBELLA</t>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
         </is>
       </c>
       <c r="AT375" t="n">
@@ -70066,47 +70055,47 @@
       </c>
       <c r="AU375" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV375" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW375" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX375" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY375" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ375" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA375" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB375" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC375" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -70133,17 +70122,17 @@
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H376" t="inlineStr">
@@ -70168,12 +70157,12 @@
       </c>
       <c r="L376" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N376" t="n">
@@ -70182,165 +70171,88 @@
       <c r="O376" t="n">
         <v>0</v>
       </c>
-      <c r="U376" t="inlineStr">
-        <is>
-          <t>SER_AU_RUBELLA</t>
-        </is>
-      </c>
-      <c r="V376" t="inlineStr">
-        <is>
-          <t>SER_AU_RUBELLA</t>
-        </is>
-      </c>
-      <c r="W376" t="inlineStr">
-        <is>
-          <t>SRC_AU_NINDSS</t>
-        </is>
-      </c>
-      <c r="X376" t="inlineStr">
-        <is>
-          <t>Rubella</t>
-        </is>
-      </c>
-      <c r="Y376" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z376" t="inlineStr">
-        <is>
-          <t>notification</t>
+      <c r="P376" t="n">
+        <v>0</v>
+      </c>
+      <c r="R376" t="n">
+        <v>0</v>
+      </c>
+      <c r="S376" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA376" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB376" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC376" t="inlineStr">
-        <is>
-          <t>country:AU:national</t>
-        </is>
-      </c>
-      <c r="AD376" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE376" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF376" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG376" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH376" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI376" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ376" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK376" t="inlineStr">
-        <is>
-          <t>Australia NINDSS rubella notifications excluding the separately reported congenital category.</t>
-        </is>
-      </c>
-      <c r="AM376" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN376" t="b">
-        <v>1</v>
+          <t>weekly</t>
+        </is>
       </c>
       <c r="AO376" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP376" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ376" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS376" t="inlineStr">
         <is>
-          <t>SER_AU_RUBELLA</t>
+          <t>SER_SG_CDA_RUBELLA; SER_SG_HIST_RUBELLA</t>
         </is>
       </c>
       <c r="AT376" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU376" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV376" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW376" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX376" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY376" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ376" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA376" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB376" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC376" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -70367,17 +70279,17 @@
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H377" t="inlineStr">
@@ -70402,12 +70314,12 @@
       </c>
       <c r="L377" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N377" t="n">
@@ -70416,23 +70328,101 @@
       <c r="O377" t="n">
         <v>0</v>
       </c>
-      <c r="R377" t="n">
-        <v>0</v>
-      </c>
-      <c r="S377" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P377" t="n">
+        <v>0</v>
       </c>
       <c r="U377" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_172</t>
+          <t>SER_SG_CDA_RUBELLA</t>
+        </is>
+      </c>
+      <c r="V377" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_RUBELLA</t>
+        </is>
+      </c>
+      <c r="W377" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X377" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="Y377" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z377" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA377" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB377" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC377" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD377" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE377" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF377" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG377" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH377" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI377" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ377" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK377" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM377" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN377" t="b">
+        <v>1</v>
       </c>
       <c r="AO377" t="inlineStr">
         <is>
@@ -70441,22 +70431,17 @@
       </c>
       <c r="AP377" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ377" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR377" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS377" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_172</t>
+          <t>SER_SG_CDA_RUBELLA; SER_SG_HIST_RUBELLA</t>
         </is>
       </c>
       <c r="AT377" t="n">
@@ -70464,47 +70449,47 @@
       </c>
       <c r="AU377" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV377" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW377" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX377" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY377" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ377" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA377" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB377" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC377" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -70531,17 +70516,17 @@
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H378" t="inlineStr">
@@ -70580,34 +70565,17 @@
       <c r="O378" t="n">
         <v>0</v>
       </c>
+      <c r="R378" t="n">
+        <v>0</v>
+      </c>
+      <c r="S378" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U378" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_172</t>
-        </is>
-      </c>
-      <c r="V378" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_172</t>
-        </is>
-      </c>
-      <c r="W378" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X378" t="inlineStr">
-        <is>
-          <t>German measles</t>
-        </is>
-      </c>
-      <c r="Y378" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z378" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>SER_AU_RUBELLA</t>
         </is>
       </c>
       <c r="AA378" t="inlineStr">
@@ -70615,135 +70583,72 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB378" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC378" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD378" t="inlineStr">
+      <c r="AO378" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP378" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ378" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS378" t="inlineStr">
+        <is>
+          <t>SER_AU_RUBELLA</t>
+        </is>
+      </c>
+      <c r="AT378" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU378" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV378" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE378" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF378" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG378" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH378" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI378" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ378" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK378" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 172.</t>
-        </is>
-      </c>
-      <c r="AM378" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN378" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO378" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP378" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ378" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR378" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS378" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_172</t>
-        </is>
-      </c>
-      <c r="AT378" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU378" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV378" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW378" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX378" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY378" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ378" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA378" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB378" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC378" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -70770,123 +70675,760 @@
       </c>
       <c r="E379" t="inlineStr">
         <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>D040</t>
+        </is>
+      </c>
+      <c r="I379" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="J379" t="inlineStr">
+        <is>
+          <t>风疹</t>
+        </is>
+      </c>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L379" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M379" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N379" t="n">
+        <v>0</v>
+      </c>
+      <c r="O379" t="n">
+        <v>0</v>
+      </c>
+      <c r="U379" t="inlineStr">
+        <is>
+          <t>SER_AU_RUBELLA</t>
+        </is>
+      </c>
+      <c r="V379" t="inlineStr">
+        <is>
+          <t>SER_AU_RUBELLA</t>
+        </is>
+      </c>
+      <c r="W379" t="inlineStr">
+        <is>
+          <t>SRC_AU_NINDSS</t>
+        </is>
+      </c>
+      <c r="X379" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="Y379" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z379" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA379" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB379" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC379" t="inlineStr">
+        <is>
+          <t>country:AU:national</t>
+        </is>
+      </c>
+      <c r="AD379" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE379" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF379" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG379" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH379" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI379" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ379" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK379" t="inlineStr">
+        <is>
+          <t>Australia NINDSS rubella notifications excluding the separately reported congenital category.</t>
+        </is>
+      </c>
+      <c r="AM379" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN379" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO379" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP379" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ379" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS379" t="inlineStr">
+        <is>
+          <t>SER_AU_RUBELLA</t>
+        </is>
+      </c>
+      <c r="AT379" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU379" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV379" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW379" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX379" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY379" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ379" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA379" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB379" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC379" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>D040</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>rubella</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
           <t>public_projection</t>
         </is>
       </c>
-      <c r="F379" t="inlineStr">
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>D040</t>
+        </is>
+      </c>
+      <c r="I380" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="J380" t="inlineStr">
+        <is>
+          <t>风疹</t>
+        </is>
+      </c>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L380" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M380" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N380" t="n">
+        <v>0</v>
+      </c>
+      <c r="O380" t="n">
+        <v>0</v>
+      </c>
+      <c r="R380" t="n">
+        <v>0</v>
+      </c>
+      <c r="S380" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U380" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_172</t>
+        </is>
+      </c>
+      <c r="AA380" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO380" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP380" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ380" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR380" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS380" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_172</t>
+        </is>
+      </c>
+      <c r="AT380" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU380" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV380" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW380" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX380" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY380" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ380" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA380" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB380" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC380" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>D040</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>rubella</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H381" t="inlineStr">
+        <is>
+          <t>D040</t>
+        </is>
+      </c>
+      <c r="I381" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="J381" t="inlineStr">
+        <is>
+          <t>风疹</t>
+        </is>
+      </c>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L381" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M381" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N381" t="n">
+        <v>0</v>
+      </c>
+      <c r="O381" t="n">
+        <v>0</v>
+      </c>
+      <c r="U381" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_172</t>
+        </is>
+      </c>
+      <c r="V381" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_172</t>
+        </is>
+      </c>
+      <c r="W381" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X381" t="inlineStr">
+        <is>
+          <t>German measles</t>
+        </is>
+      </c>
+      <c r="Y381" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z381" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA381" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB381" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC381" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD381" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE381" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF381" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG381" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH381" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI381" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ381" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK381" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 172.</t>
+        </is>
+      </c>
+      <c r="AM381" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN381" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO381" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP381" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ381" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR381" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS381" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_172</t>
+        </is>
+      </c>
+      <c r="AT381" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU381" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV381" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW381" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX381" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY381" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ381" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA381" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB381" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC381" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>D040</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>rubella</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
         <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="G379" t="inlineStr">
+      <c r="G382" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="H379" t="inlineStr">
-        <is>
-          <t>D040</t>
-        </is>
-      </c>
-      <c r="I379" t="inlineStr">
-        <is>
-          <t>Rubella</t>
-        </is>
-      </c>
-      <c r="J379" t="inlineStr">
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>D040</t>
+        </is>
+      </c>
+      <c r="I382" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="J382" t="inlineStr">
         <is>
           <t>风疹</t>
         </is>
       </c>
-      <c r="K379" t="inlineStr">
+      <c r="K382" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L379" t="inlineStr">
+      <c r="L382" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="M379" t="inlineStr">
+      <c r="M382" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N379" t="n">
-        <v>0</v>
-      </c>
-      <c r="O379" t="n">
-        <v>0</v>
-      </c>
-      <c r="R379" t="n">
-        <v>0</v>
-      </c>
-      <c r="S379" t="inlineStr">
+      <c r="N382" t="n">
+        <v>0</v>
+      </c>
+      <c r="O382" t="n">
+        <v>0</v>
+      </c>
+      <c r="R382" t="n">
+        <v>0</v>
+      </c>
+      <c r="S382" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO379" t="inlineStr">
+      <c r="AO382" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP379" t="inlineStr">
+      <c r="AP382" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR379" t="inlineStr">
+      <c r="AR382" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS379" t="inlineStr"/>
-      <c r="AT379" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU379" t="inlineStr">
+      <c r="AS382" t="inlineStr"/>
+      <c r="AT382" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU382" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV379" t="inlineStr">
+      <c r="AV382" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW379" t="inlineStr">
+      <c r="AW382" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX379" t="inlineStr">
+      <c r="AX382" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY379" t="inlineStr">
+      <c r="AY382" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ379" t="inlineStr">
+      <c r="AZ382" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA379" t="inlineStr">
+      <c r="BA382" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB379" t="inlineStr">
+      <c r="BB382" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC379" t="inlineStr">
+      <c r="BC382" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -71008,7 +71550,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="10">
@@ -71018,7 +71560,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="11">
@@ -71038,7 +71580,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="13">
@@ -71070,7 +71612,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>399</v>
+        <v>443</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d040/2026-2029.xlsx
+++ b/diseases/d040/2026-2029.xlsx
@@ -71434,6 +71434,405 @@
         </is>
       </c>
     </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>D040</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>rubella</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>D040</t>
+        </is>
+      </c>
+      <c r="I383" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="J383" t="inlineStr">
+        <is>
+          <t>风疹</t>
+        </is>
+      </c>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L383" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M383" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N383" t="n">
+        <v>0</v>
+      </c>
+      <c r="O383" t="n">
+        <v>0</v>
+      </c>
+      <c r="P383" t="n">
+        <v>0</v>
+      </c>
+      <c r="R383" t="n">
+        <v>0</v>
+      </c>
+      <c r="S383" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U383" t="inlineStr">
+        <is>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA383" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO383" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP383" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ383" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS383" t="inlineStr">
+        <is>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT383" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU383" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV383" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW383" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX383" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY383" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ383" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA383" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB383" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC383" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>D040</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>rubella</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>D040</t>
+        </is>
+      </c>
+      <c r="I384" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="J384" t="inlineStr">
+        <is>
+          <t>风疹</t>
+        </is>
+      </c>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L384" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M384" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N384" t="n">
+        <v>0</v>
+      </c>
+      <c r="O384" t="n">
+        <v>0</v>
+      </c>
+      <c r="P384" t="n">
+        <v>0</v>
+      </c>
+      <c r="U384" t="inlineStr">
+        <is>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V384" t="inlineStr">
+        <is>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W384" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X384" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="Y384" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z384" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA384" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB384" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC384" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD384" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE384" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF384" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG384" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH384" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI384" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ384" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK384" t="inlineStr">
+        <is>
+          <t>Japan NIID rubella notifications, excluding congenital rubella syndrome.</t>
+        </is>
+      </c>
+      <c r="AM384" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN384" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO384" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP384" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ384" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS384" t="inlineStr">
+        <is>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT384" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU384" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV384" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW384" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX384" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY384" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ384" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA384" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB384" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC384" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -71467,7 +71866,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -71550,7 +71949,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="10">
@@ -71560,7 +71959,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="11">
@@ -71580,7 +71979,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d040/2026-2029.xlsx
+++ b/diseases/d040/2026-2029.xlsx
@@ -71833,6 +71833,400 @@
         </is>
       </c>
     </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>D040</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>rubella</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>D040</t>
+        </is>
+      </c>
+      <c r="I385" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="J385" t="inlineStr">
+        <is>
+          <t>风疹</t>
+        </is>
+      </c>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L385" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M385" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N385" t="n">
+        <v>0</v>
+      </c>
+      <c r="O385" t="n">
+        <v>0</v>
+      </c>
+      <c r="P385" t="n">
+        <v>0</v>
+      </c>
+      <c r="R385" t="n">
+        <v>0</v>
+      </c>
+      <c r="S385" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA385" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO385" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP385" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ385" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS385" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_RUBELLA; SER_SG_HIST_RUBELLA</t>
+        </is>
+      </c>
+      <c r="AT385" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU385" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV385" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW385" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX385" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY385" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ385" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA385" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB385" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC385" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>D040</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>rubella</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H386" t="inlineStr">
+        <is>
+          <t>D040</t>
+        </is>
+      </c>
+      <c r="I386" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="J386" t="inlineStr">
+        <is>
+          <t>风疹</t>
+        </is>
+      </c>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L386" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M386" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N386" t="n">
+        <v>0</v>
+      </c>
+      <c r="O386" t="n">
+        <v>0</v>
+      </c>
+      <c r="P386" t="n">
+        <v>0</v>
+      </c>
+      <c r="U386" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_RUBELLA</t>
+        </is>
+      </c>
+      <c r="V386" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_RUBELLA</t>
+        </is>
+      </c>
+      <c r="W386" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X386" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="Y386" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z386" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA386" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB386" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC386" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD386" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE386" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF386" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG386" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH386" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI386" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ386" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK386" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM386" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN386" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO386" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP386" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ386" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS386" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_RUBELLA; SER_SG_HIST_RUBELLA</t>
+        </is>
+      </c>
+      <c r="AT386" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU386" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV386" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW386" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX386" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY386" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ386" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA386" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB386" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC386" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -71949,7 +72343,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="10">
@@ -71959,7 +72353,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="11">
@@ -71979,7 +72373,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d040/2026-2029.xlsx
+++ b/diseases/d040/2026-2029.xlsx
@@ -6026,7 +6026,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -6967,7 +6967,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7908,7 +7908,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -8849,7 +8849,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -14113,7 +14113,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15602,7 +15602,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16543,7 +16543,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
@@ -17484,7 +17484,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -22363,7 +22363,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -23852,7 +23852,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -24793,7 +24793,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
@@ -25734,7 +25734,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -26675,7 +26675,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK140" t="inlineStr">
@@ -32099,7 +32099,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -33040,7 +33040,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK174" t="inlineStr">
@@ -33981,7 +33981,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -34922,7 +34922,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK184" t="inlineStr">
@@ -40731,7 +40731,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
@@ -41672,7 +41672,7 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK220" t="inlineStr">
@@ -42613,7 +42613,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
@@ -43554,7 +43554,7 @@
       </c>
       <c r="AJ230" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK230" t="inlineStr">
@@ -44495,7 +44495,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -45282,7 +45282,7 @@
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">
@@ -51286,7 +51286,7 @@
       </c>
       <c r="AJ273" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK273" t="inlineStr">
@@ -52224,7 +52224,7 @@
       </c>
       <c r="AJ278" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK278" t="inlineStr">
@@ -53162,7 +53162,7 @@
       </c>
       <c r="AJ283" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK283" t="inlineStr">
@@ -54100,7 +54100,7 @@
       </c>
       <c r="AJ288" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK288" t="inlineStr">
@@ -54887,7 +54887,7 @@
       </c>
       <c r="AJ292" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK292" t="inlineStr">
@@ -60749,7 +60749,7 @@
       </c>
       <c r="AJ325" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK325" t="inlineStr">
@@ -61687,7 +61687,7 @@
       </c>
       <c r="AJ330" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK330" t="inlineStr">
@@ -62625,7 +62625,7 @@
       </c>
       <c r="AJ335" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK335" t="inlineStr">
@@ -63563,7 +63563,7 @@
       </c>
       <c r="AJ340" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK340" t="inlineStr">
@@ -64350,7 +64350,7 @@
       </c>
       <c r="AJ344" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK344" t="inlineStr">
@@ -66008,12 +66008,12 @@
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
@@ -66086,42 +66086,42 @@
       </c>
       <c r="AV355" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW355" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX355" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY355" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ355" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA355" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB355" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC355" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -66153,12 +66153,12 @@
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
@@ -66205,87 +66205,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U356" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_RUBELLA</t>
-        </is>
-      </c>
-      <c r="AA356" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO356" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP356" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ356" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR356" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS356" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_RUBELLA</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS356" t="inlineStr"/>
       <c r="AT356" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU356" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV356" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW356" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX356" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY356" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ356" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA356" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB356" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC356" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -66312,7 +66293,7 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
@@ -66361,98 +66342,23 @@
       <c r="O357" t="n">
         <v>0</v>
       </c>
+      <c r="R357" t="n">
+        <v>0</v>
+      </c>
+      <c r="S357" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U357" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_RUBELLA</t>
         </is>
       </c>
-      <c r="V357" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_RUBELLA</t>
-        </is>
-      </c>
-      <c r="W357" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X357" t="inlineStr">
-        <is>
-          <t>Röda hund</t>
-        </is>
-      </c>
-      <c r="Y357" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z357" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA357" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB357" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC357" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD357" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE357" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF357" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG357" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH357" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI357" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ357" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK357" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; Excludes congenital rubella syndrome unless source definition changes.</t>
-        </is>
-      </c>
-      <c r="AM357" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN357" t="b">
-        <v>1</v>
       </c>
       <c r="AO357" t="inlineStr">
         <is>
@@ -66551,17 +66457,17 @@
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H358" t="inlineStr">
@@ -66586,7 +66492,7 @@
       </c>
       <c r="L358" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M358" t="inlineStr">
@@ -66600,26 +66506,98 @@
       <c r="O358" t="n">
         <v>0</v>
       </c>
-      <c r="P358" t="n">
-        <v>0</v>
-      </c>
-      <c r="R358" t="n">
-        <v>0</v>
-      </c>
-      <c r="S358" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U358" t="inlineStr">
         <is>
-          <t>SER_JP_RUBELLA_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_RUBELLA</t>
+        </is>
+      </c>
+      <c r="V358" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_RUBELLA</t>
+        </is>
+      </c>
+      <c r="W358" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X358" t="inlineStr">
+        <is>
+          <t>Röda hund</t>
+        </is>
+      </c>
+      <c r="Y358" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z358" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA358" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB358" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC358" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD358" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE358" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF358" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG358" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH358" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI358" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ358" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK358" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; Excludes congenital rubella syndrome unless source definition changes.</t>
+        </is>
+      </c>
+      <c r="AM358" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN358" t="b">
+        <v>1</v>
       </c>
       <c r="AO358" t="inlineStr">
         <is>
@@ -66628,7 +66606,7 @@
       </c>
       <c r="AP358" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ358" t="inlineStr">
@@ -66636,57 +66614,62 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR358" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS358" t="inlineStr">
         <is>
-          <t>SER_JP_RUBELLA_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_RUBELLA</t>
         </is>
       </c>
       <c r="AT358" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU358" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV358" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW358" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX358" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY358" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ358" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA358" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB358" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC358" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -66713,7 +66696,7 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
@@ -66765,98 +66748,23 @@
       <c r="P359" t="n">
         <v>0</v>
       </c>
+      <c r="R359" t="n">
+        <v>0</v>
+      </c>
+      <c r="S359" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U359" t="inlineStr">
         <is>
           <t>SER_JP_RUBELLA_WEEKLY</t>
         </is>
       </c>
-      <c r="V359" t="inlineStr">
-        <is>
-          <t>SER_JP_RUBELLA_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W359" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X359" t="inlineStr">
-        <is>
-          <t>Rubella</t>
-        </is>
-      </c>
-      <c r="Y359" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z359" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA359" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB359" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC359" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD359" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE359" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF359" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG359" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH359" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI359" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ359" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK359" t="inlineStr">
-        <is>
-          <t>Japan NIID rubella notifications, excluding congenital rubella syndrome.</t>
-        </is>
-      </c>
-      <c r="AM359" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN359" t="b">
-        <v>1</v>
       </c>
       <c r="AO359" t="inlineStr">
         <is>
@@ -66950,17 +66858,17 @@
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H360" t="inlineStr">
@@ -67002,12 +66910,34 @@
       <c r="P360" t="n">
         <v>0</v>
       </c>
-      <c r="R360" t="n">
-        <v>0</v>
-      </c>
-      <c r="S360" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U360" t="inlineStr">
+        <is>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V360" t="inlineStr">
+        <is>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W360" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X360" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="Y360" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z360" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA360" t="inlineStr">
@@ -67015,6 +66945,64 @@
           <t>weekly</t>
         </is>
       </c>
+      <c r="AB360" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC360" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD360" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE360" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF360" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG360" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH360" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI360" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ360" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK360" t="inlineStr">
+        <is>
+          <t>Japan NIID rubella notifications, excluding congenital rubella syndrome.</t>
+        </is>
+      </c>
+      <c r="AM360" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN360" t="b">
+        <v>1</v>
+      </c>
       <c r="AO360" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -67022,7 +67010,7 @@
       </c>
       <c r="AP360" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ360" t="inlineStr">
@@ -67032,55 +67020,55 @@
       </c>
       <c r="AS360" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_RUBELLA; SER_SG_HIST_RUBELLA</t>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
         </is>
       </c>
       <c r="AT360" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU360" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV360" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW360" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX360" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY360" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ360" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA360" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB360" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC360" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -67107,7 +67095,7 @@
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
@@ -67159,98 +67147,18 @@
       <c r="P361" t="n">
         <v>0</v>
       </c>
-      <c r="U361" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_RUBELLA</t>
-        </is>
-      </c>
-      <c r="V361" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_RUBELLA</t>
-        </is>
-      </c>
-      <c r="W361" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X361" t="inlineStr">
-        <is>
-          <t>Rubella</t>
-        </is>
-      </c>
-      <c r="Y361" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z361" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R361" t="n">
+        <v>0</v>
+      </c>
+      <c r="S361" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA361" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB361" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC361" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD361" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE361" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF361" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG361" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH361" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI361" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ361" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK361" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM361" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN361" t="b">
-        <v>1</v>
       </c>
       <c r="AO361" t="inlineStr">
         <is>
@@ -67344,17 +67252,17 @@
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
@@ -67379,7 +67287,7 @@
       </c>
       <c r="L362" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M362" t="inlineStr">
@@ -67396,17 +67304,34 @@
       <c r="P362" t="n">
         <v>0</v>
       </c>
-      <c r="R362" t="n">
-        <v>0</v>
-      </c>
-      <c r="S362" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U362" t="inlineStr">
         <is>
-          <t>SER_JP_RUBELLA_WEEKLY</t>
+          <t>SER_SG_CDA_RUBELLA</t>
+        </is>
+      </c>
+      <c r="V362" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_RUBELLA</t>
+        </is>
+      </c>
+      <c r="W362" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X362" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="Y362" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z362" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA362" t="inlineStr">
@@ -67414,6 +67339,64 @@
           <t>weekly</t>
         </is>
       </c>
+      <c r="AB362" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC362" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD362" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE362" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF362" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG362" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH362" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI362" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ362" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK362" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM362" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN362" t="b">
+        <v>1</v>
+      </c>
       <c r="AO362" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -67421,7 +67404,7 @@
       </c>
       <c r="AP362" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ362" t="inlineStr">
@@ -67431,55 +67414,55 @@
       </c>
       <c r="AS362" t="inlineStr">
         <is>
-          <t>SER_JP_RUBELLA_WEEKLY</t>
+          <t>SER_SG_CDA_RUBELLA; SER_SG_HIST_RUBELLA</t>
         </is>
       </c>
       <c r="AT362" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU362" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV362" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW362" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX362" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY362" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ362" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA362" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB362" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC362" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -67506,7 +67489,7 @@
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
@@ -67558,98 +67541,23 @@
       <c r="P363" t="n">
         <v>0</v>
       </c>
+      <c r="R363" t="n">
+        <v>0</v>
+      </c>
+      <c r="S363" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U363" t="inlineStr">
         <is>
           <t>SER_JP_RUBELLA_WEEKLY</t>
         </is>
       </c>
-      <c r="V363" t="inlineStr">
-        <is>
-          <t>SER_JP_RUBELLA_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W363" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X363" t="inlineStr">
-        <is>
-          <t>Rubella</t>
-        </is>
-      </c>
-      <c r="Y363" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z363" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA363" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB363" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC363" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD363" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE363" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF363" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG363" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH363" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI363" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ363" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK363" t="inlineStr">
-        <is>
-          <t>Japan NIID rubella notifications, excluding congenital rubella syndrome.</t>
-        </is>
-      </c>
-      <c r="AM363" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN363" t="b">
-        <v>1</v>
       </c>
       <c r="AO363" t="inlineStr">
         <is>
@@ -67743,17 +67651,17 @@
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
@@ -67795,12 +67703,34 @@
       <c r="P364" t="n">
         <v>0</v>
       </c>
-      <c r="R364" t="n">
-        <v>0</v>
-      </c>
-      <c r="S364" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U364" t="inlineStr">
+        <is>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V364" t="inlineStr">
+        <is>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W364" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X364" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="Y364" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z364" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA364" t="inlineStr">
@@ -67808,6 +67738,64 @@
           <t>weekly</t>
         </is>
       </c>
+      <c r="AB364" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC364" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD364" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE364" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF364" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG364" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH364" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI364" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ364" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK364" t="inlineStr">
+        <is>
+          <t>Japan NIID rubella notifications, excluding congenital rubella syndrome.</t>
+        </is>
+      </c>
+      <c r="AM364" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN364" t="b">
+        <v>1</v>
+      </c>
       <c r="AO364" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -67815,7 +67803,7 @@
       </c>
       <c r="AP364" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ364" t="inlineStr">
@@ -67825,55 +67813,55 @@
       </c>
       <c r="AS364" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_RUBELLA; SER_SG_HIST_RUBELLA</t>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
         </is>
       </c>
       <c r="AT364" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU364" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV364" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW364" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX364" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY364" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ364" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA364" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB364" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC364" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -67900,7 +67888,7 @@
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
@@ -67952,98 +67940,18 @@
       <c r="P365" t="n">
         <v>0</v>
       </c>
-      <c r="U365" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_RUBELLA</t>
-        </is>
-      </c>
-      <c r="V365" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_RUBELLA</t>
-        </is>
-      </c>
-      <c r="W365" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X365" t="inlineStr">
-        <is>
-          <t>Rubella</t>
-        </is>
-      </c>
-      <c r="Y365" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z365" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R365" t="n">
+        <v>0</v>
+      </c>
+      <c r="S365" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA365" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB365" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC365" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD365" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE365" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF365" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG365" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH365" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI365" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ365" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK365" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM365" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN365" t="b">
-        <v>1</v>
       </c>
       <c r="AO365" t="inlineStr">
         <is>
@@ -68137,17 +68045,17 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H366" t="inlineStr">
@@ -68172,7 +68080,7 @@
       </c>
       <c r="L366" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M366" t="inlineStr">
@@ -68189,17 +68097,34 @@
       <c r="P366" t="n">
         <v>0</v>
       </c>
-      <c r="R366" t="n">
-        <v>0</v>
-      </c>
-      <c r="S366" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U366" t="inlineStr">
         <is>
-          <t>SER_JP_RUBELLA_WEEKLY</t>
+          <t>SER_SG_CDA_RUBELLA</t>
+        </is>
+      </c>
+      <c r="V366" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_RUBELLA</t>
+        </is>
+      </c>
+      <c r="W366" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X366" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="Y366" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z366" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA366" t="inlineStr">
@@ -68207,6 +68132,64 @@
           <t>weekly</t>
         </is>
       </c>
+      <c r="AB366" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC366" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD366" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE366" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF366" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG366" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH366" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI366" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ366" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK366" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM366" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN366" t="b">
+        <v>1</v>
+      </c>
       <c r="AO366" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -68214,7 +68197,7 @@
       </c>
       <c r="AP366" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ366" t="inlineStr">
@@ -68224,55 +68207,55 @@
       </c>
       <c r="AS366" t="inlineStr">
         <is>
-          <t>SER_JP_RUBELLA_WEEKLY</t>
+          <t>SER_SG_CDA_RUBELLA; SER_SG_HIST_RUBELLA</t>
         </is>
       </c>
       <c r="AT366" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU366" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV366" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW366" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX366" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY366" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ366" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA366" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB366" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC366" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -68299,7 +68282,7 @@
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
@@ -68351,98 +68334,23 @@
       <c r="P367" t="n">
         <v>0</v>
       </c>
+      <c r="R367" t="n">
+        <v>0</v>
+      </c>
+      <c r="S367" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U367" t="inlineStr">
         <is>
           <t>SER_JP_RUBELLA_WEEKLY</t>
         </is>
       </c>
-      <c r="V367" t="inlineStr">
-        <is>
-          <t>SER_JP_RUBELLA_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W367" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X367" t="inlineStr">
-        <is>
-          <t>Rubella</t>
-        </is>
-      </c>
-      <c r="Y367" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z367" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA367" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB367" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC367" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD367" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE367" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF367" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG367" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH367" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI367" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ367" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK367" t="inlineStr">
-        <is>
-          <t>Japan NIID rubella notifications, excluding congenital rubella syndrome.</t>
-        </is>
-      </c>
-      <c r="AM367" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN367" t="b">
-        <v>1</v>
       </c>
       <c r="AO367" t="inlineStr">
         <is>
@@ -68536,17 +68444,17 @@
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H368" t="inlineStr">
@@ -68588,12 +68496,34 @@
       <c r="P368" t="n">
         <v>0</v>
       </c>
-      <c r="R368" t="n">
-        <v>0</v>
-      </c>
-      <c r="S368" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U368" t="inlineStr">
+        <is>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V368" t="inlineStr">
+        <is>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W368" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X368" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="Y368" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z368" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA368" t="inlineStr">
@@ -68601,6 +68531,64 @@
           <t>weekly</t>
         </is>
       </c>
+      <c r="AB368" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC368" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD368" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE368" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF368" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG368" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH368" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI368" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ368" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK368" t="inlineStr">
+        <is>
+          <t>Japan NIID rubella notifications, excluding congenital rubella syndrome.</t>
+        </is>
+      </c>
+      <c r="AM368" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN368" t="b">
+        <v>1</v>
+      </c>
       <c r="AO368" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -68608,7 +68596,7 @@
       </c>
       <c r="AP368" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ368" t="inlineStr">
@@ -68618,55 +68606,55 @@
       </c>
       <c r="AS368" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_RUBELLA; SER_SG_HIST_RUBELLA</t>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
         </is>
       </c>
       <c r="AT368" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU368" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV368" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW368" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX368" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY368" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ368" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA368" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB368" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC368" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -68693,7 +68681,7 @@
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
@@ -68745,98 +68733,18 @@
       <c r="P369" t="n">
         <v>0</v>
       </c>
-      <c r="U369" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_RUBELLA</t>
-        </is>
-      </c>
-      <c r="V369" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_RUBELLA</t>
-        </is>
-      </c>
-      <c r="W369" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X369" t="inlineStr">
-        <is>
-          <t>Rubella</t>
-        </is>
-      </c>
-      <c r="Y369" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z369" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R369" t="n">
+        <v>0</v>
+      </c>
+      <c r="S369" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA369" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB369" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC369" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD369" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE369" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF369" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG369" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH369" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI369" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ369" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK369" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM369" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN369" t="b">
-        <v>1</v>
       </c>
       <c r="AO369" t="inlineStr">
         <is>
@@ -68930,17 +68838,17 @@
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H370" t="inlineStr">
@@ -68965,7 +68873,7 @@
       </c>
       <c r="L370" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M370" t="inlineStr">
@@ -68982,17 +68890,34 @@
       <c r="P370" t="n">
         <v>0</v>
       </c>
-      <c r="R370" t="n">
-        <v>0</v>
-      </c>
-      <c r="S370" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U370" t="inlineStr">
         <is>
-          <t>SER_JP_RUBELLA_WEEKLY</t>
+          <t>SER_SG_CDA_RUBELLA</t>
+        </is>
+      </c>
+      <c r="V370" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_RUBELLA</t>
+        </is>
+      </c>
+      <c r="W370" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X370" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="Y370" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z370" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA370" t="inlineStr">
@@ -69000,6 +68925,64 @@
           <t>weekly</t>
         </is>
       </c>
+      <c r="AB370" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC370" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD370" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE370" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF370" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG370" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH370" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI370" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ370" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK370" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM370" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN370" t="b">
+        <v>1</v>
+      </c>
       <c r="AO370" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -69007,7 +68990,7 @@
       </c>
       <c r="AP370" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ370" t="inlineStr">
@@ -69017,55 +69000,55 @@
       </c>
       <c r="AS370" t="inlineStr">
         <is>
-          <t>SER_JP_RUBELLA_WEEKLY</t>
+          <t>SER_SG_CDA_RUBELLA; SER_SG_HIST_RUBELLA</t>
         </is>
       </c>
       <c r="AT370" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU370" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV370" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW370" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX370" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY370" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ370" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA370" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB370" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC370" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -69092,7 +69075,7 @@
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
@@ -69144,98 +69127,23 @@
       <c r="P371" t="n">
         <v>0</v>
       </c>
+      <c r="R371" t="n">
+        <v>0</v>
+      </c>
+      <c r="S371" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U371" t="inlineStr">
         <is>
           <t>SER_JP_RUBELLA_WEEKLY</t>
         </is>
       </c>
-      <c r="V371" t="inlineStr">
-        <is>
-          <t>SER_JP_RUBELLA_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W371" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X371" t="inlineStr">
-        <is>
-          <t>Rubella</t>
-        </is>
-      </c>
-      <c r="Y371" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z371" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA371" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB371" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC371" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD371" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE371" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF371" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG371" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH371" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI371" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ371" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK371" t="inlineStr">
-        <is>
-          <t>Japan NIID rubella notifications, excluding congenital rubella syndrome.</t>
-        </is>
-      </c>
-      <c r="AM371" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN371" t="b">
-        <v>1</v>
       </c>
       <c r="AO371" t="inlineStr">
         <is>
@@ -69329,17 +69237,17 @@
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H372" t="inlineStr">
@@ -69381,12 +69289,34 @@
       <c r="P372" t="n">
         <v>0</v>
       </c>
-      <c r="R372" t="n">
-        <v>0</v>
-      </c>
-      <c r="S372" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U372" t="inlineStr">
+        <is>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V372" t="inlineStr">
+        <is>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W372" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X372" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="Y372" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z372" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA372" t="inlineStr">
@@ -69394,6 +69324,64 @@
           <t>weekly</t>
         </is>
       </c>
+      <c r="AB372" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC372" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD372" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE372" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF372" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG372" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH372" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI372" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ372" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK372" t="inlineStr">
+        <is>
+          <t>Japan NIID rubella notifications, excluding congenital rubella syndrome.</t>
+        </is>
+      </c>
+      <c r="AM372" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN372" t="b">
+        <v>1</v>
+      </c>
       <c r="AO372" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -69401,7 +69389,7 @@
       </c>
       <c r="AP372" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ372" t="inlineStr">
@@ -69411,55 +69399,55 @@
       </c>
       <c r="AS372" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_RUBELLA; SER_SG_HIST_RUBELLA</t>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
         </is>
       </c>
       <c r="AT372" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU372" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV372" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW372" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX372" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY372" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ372" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA372" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB372" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC372" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -69486,7 +69474,7 @@
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F373" t="inlineStr">
@@ -69538,98 +69526,18 @@
       <c r="P373" t="n">
         <v>0</v>
       </c>
-      <c r="U373" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_RUBELLA</t>
-        </is>
-      </c>
-      <c r="V373" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_RUBELLA</t>
-        </is>
-      </c>
-      <c r="W373" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X373" t="inlineStr">
-        <is>
-          <t>Rubella</t>
-        </is>
-      </c>
-      <c r="Y373" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z373" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R373" t="n">
+        <v>0</v>
+      </c>
+      <c r="S373" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA373" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB373" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC373" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD373" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE373" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF373" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG373" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH373" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI373" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ373" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK373" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM373" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN373" t="b">
-        <v>1</v>
       </c>
       <c r="AO373" t="inlineStr">
         <is>
@@ -69723,17 +69631,17 @@
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
@@ -69758,7 +69666,7 @@
       </c>
       <c r="L374" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M374" t="inlineStr">
@@ -69767,32 +69675,107 @@
         </is>
       </c>
       <c r="N374" t="n">
+        <v>0</v>
+      </c>
+      <c r="O374" t="n">
+        <v>0</v>
+      </c>
+      <c r="P374" t="n">
+        <v>0</v>
+      </c>
+      <c r="U374" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_RUBELLA</t>
+        </is>
+      </c>
+      <c r="V374" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_RUBELLA</t>
+        </is>
+      </c>
+      <c r="W374" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X374" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="Y374" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z374" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA374" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB374" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC374" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD374" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE374" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF374" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG374" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH374" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI374" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ374" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK374" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM374" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN374" t="b">
         <v>1</v>
       </c>
-      <c r="O374" t="n">
-        <v>1</v>
-      </c>
-      <c r="P374" t="n">
-        <v>1</v>
-      </c>
-      <c r="R374" t="n">
-        <v>0.0008168084075657662</v>
-      </c>
-      <c r="S374" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U374" t="inlineStr">
-        <is>
-          <t>SER_JP_RUBELLA_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA374" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO374" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -69800,7 +69783,7 @@
       </c>
       <c r="AP374" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ374" t="inlineStr">
@@ -69810,55 +69793,55 @@
       </c>
       <c r="AS374" t="inlineStr">
         <is>
-          <t>SER_JP_RUBELLA_WEEKLY</t>
+          <t>SER_SG_CDA_RUBELLA; SER_SG_HIST_RUBELLA</t>
         </is>
       </c>
       <c r="AT374" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU374" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV374" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW374" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX374" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY374" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ374" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA374" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB374" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC374" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -69885,7 +69868,7 @@
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
@@ -69937,98 +69920,23 @@
       <c r="P375" t="n">
         <v>1</v>
       </c>
+      <c r="R375" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S375" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U375" t="inlineStr">
         <is>
           <t>SER_JP_RUBELLA_WEEKLY</t>
         </is>
       </c>
-      <c r="V375" t="inlineStr">
-        <is>
-          <t>SER_JP_RUBELLA_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W375" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X375" t="inlineStr">
-        <is>
-          <t>Rubella</t>
-        </is>
-      </c>
-      <c r="Y375" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z375" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA375" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB375" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC375" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD375" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE375" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF375" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG375" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH375" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI375" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ375" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK375" t="inlineStr">
-        <is>
-          <t>Japan NIID rubella notifications, excluding congenital rubella syndrome.</t>
-        </is>
-      </c>
-      <c r="AM375" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN375" t="b">
-        <v>1</v>
       </c>
       <c r="AO375" t="inlineStr">
         <is>
@@ -70122,17 +70030,17 @@
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H376" t="inlineStr">
@@ -70166,20 +70074,42 @@
         </is>
       </c>
       <c r="N376" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O376" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P376" t="n">
-        <v>0</v>
-      </c>
-      <c r="R376" t="n">
-        <v>0</v>
-      </c>
-      <c r="S376" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>1</v>
+      </c>
+      <c r="U376" t="inlineStr">
+        <is>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V376" t="inlineStr">
+        <is>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W376" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X376" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="Y376" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z376" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA376" t="inlineStr">
@@ -70187,6 +70117,64 @@
           <t>weekly</t>
         </is>
       </c>
+      <c r="AB376" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC376" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD376" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE376" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF376" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG376" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH376" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI376" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ376" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK376" t="inlineStr">
+        <is>
+          <t>Japan NIID rubella notifications, excluding congenital rubella syndrome.</t>
+        </is>
+      </c>
+      <c r="AM376" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN376" t="b">
+        <v>1</v>
+      </c>
       <c r="AO376" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -70194,7 +70182,7 @@
       </c>
       <c r="AP376" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ376" t="inlineStr">
@@ -70204,55 +70192,55 @@
       </c>
       <c r="AS376" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_RUBELLA; SER_SG_HIST_RUBELLA</t>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
         </is>
       </c>
       <c r="AT376" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU376" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV376" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW376" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX376" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY376" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ376" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA376" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB376" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC376" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -70279,7 +70267,7 @@
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F377" t="inlineStr">
@@ -70331,98 +70319,18 @@
       <c r="P377" t="n">
         <v>0</v>
       </c>
-      <c r="U377" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_RUBELLA</t>
-        </is>
-      </c>
-      <c r="V377" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_RUBELLA</t>
-        </is>
-      </c>
-      <c r="W377" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X377" t="inlineStr">
-        <is>
-          <t>Rubella</t>
-        </is>
-      </c>
-      <c r="Y377" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z377" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R377" t="n">
+        <v>0</v>
+      </c>
+      <c r="S377" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA377" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB377" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC377" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD377" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE377" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF377" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG377" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH377" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI377" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ377" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK377" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM377" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN377" t="b">
-        <v>1</v>
       </c>
       <c r="AO377" t="inlineStr">
         <is>
@@ -70516,17 +70424,17 @@
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H378" t="inlineStr">
@@ -70551,12 +70459,12 @@
       </c>
       <c r="L378" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N378" t="n">
@@ -70565,90 +70473,168 @@
       <c r="O378" t="n">
         <v>0</v>
       </c>
-      <c r="R378" t="n">
-        <v>0</v>
-      </c>
-      <c r="S378" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P378" t="n">
+        <v>0</v>
       </c>
       <c r="U378" t="inlineStr">
         <is>
-          <t>SER_AU_RUBELLA</t>
+          <t>SER_SG_CDA_RUBELLA</t>
+        </is>
+      </c>
+      <c r="V378" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_RUBELLA</t>
+        </is>
+      </c>
+      <c r="W378" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X378" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="Y378" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z378" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA378" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB378" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC378" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD378" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE378" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF378" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG378" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH378" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI378" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ378" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK378" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM378" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN378" t="b">
+        <v>1</v>
       </c>
       <c r="AO378" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP378" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ378" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS378" t="inlineStr">
         <is>
-          <t>SER_AU_RUBELLA</t>
+          <t>SER_SG_CDA_RUBELLA; SER_SG_HIST_RUBELLA</t>
         </is>
       </c>
       <c r="AT378" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU378" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV378" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW378" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX378" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY378" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ378" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA378" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB378" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC378" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -70675,7 +70661,7 @@
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F379" t="inlineStr">
@@ -70724,98 +70710,23 @@
       <c r="O379" t="n">
         <v>0</v>
       </c>
+      <c r="R379" t="n">
+        <v>0</v>
+      </c>
+      <c r="S379" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U379" t="inlineStr">
         <is>
           <t>SER_AU_RUBELLA</t>
         </is>
       </c>
-      <c r="V379" t="inlineStr">
-        <is>
-          <t>SER_AU_RUBELLA</t>
-        </is>
-      </c>
-      <c r="W379" t="inlineStr">
-        <is>
-          <t>SRC_AU_NINDSS</t>
-        </is>
-      </c>
-      <c r="X379" t="inlineStr">
-        <is>
-          <t>Rubella</t>
-        </is>
-      </c>
-      <c r="Y379" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z379" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA379" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB379" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC379" t="inlineStr">
-        <is>
-          <t>country:AU:national</t>
-        </is>
-      </c>
-      <c r="AD379" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE379" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF379" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG379" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH379" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI379" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ379" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK379" t="inlineStr">
-        <is>
-          <t>Australia NINDSS rubella notifications excluding the separately reported congenital category.</t>
-        </is>
-      </c>
-      <c r="AM379" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN379" t="b">
-        <v>1</v>
       </c>
       <c r="AO379" t="inlineStr">
         <is>
@@ -70909,17 +70820,17 @@
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H380" t="inlineStr">
@@ -70958,17 +70869,34 @@
       <c r="O380" t="n">
         <v>0</v>
       </c>
-      <c r="R380" t="n">
-        <v>0</v>
-      </c>
-      <c r="S380" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U380" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_172</t>
+          <t>SER_AU_RUBELLA</t>
+        </is>
+      </c>
+      <c r="V380" t="inlineStr">
+        <is>
+          <t>SER_AU_RUBELLA</t>
+        </is>
+      </c>
+      <c r="W380" t="inlineStr">
+        <is>
+          <t>SRC_AU_NINDSS</t>
+        </is>
+      </c>
+      <c r="X380" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="Y380" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z380" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA380" t="inlineStr">
@@ -70976,77 +70904,130 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB380" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC380" t="inlineStr">
+        <is>
+          <t>country:AU:national</t>
+        </is>
+      </c>
+      <c r="AD380" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE380" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF380" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG380" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH380" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI380" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ380" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK380" t="inlineStr">
+        <is>
+          <t>Australia NINDSS rubella notifications excluding the separately reported congenital category.</t>
+        </is>
+      </c>
+      <c r="AM380" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN380" t="b">
+        <v>1</v>
+      </c>
       <c r="AO380" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP380" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ380" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR380" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS380" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_172</t>
+          <t>SER_AU_RUBELLA</t>
         </is>
       </c>
       <c r="AT380" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU380" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV380" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW380" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX380" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY380" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ380" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA380" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB380" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC380" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -71073,7 +71054,7 @@
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F381" t="inlineStr">
@@ -71122,98 +71103,23 @@
       <c r="O381" t="n">
         <v>0</v>
       </c>
+      <c r="R381" t="n">
+        <v>0</v>
+      </c>
+      <c r="S381" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U381" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_172</t>
         </is>
       </c>
-      <c r="V381" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_172</t>
-        </is>
-      </c>
-      <c r="W381" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X381" t="inlineStr">
-        <is>
-          <t>German measles</t>
-        </is>
-      </c>
-      <c r="Y381" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z381" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA381" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB381" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC381" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD381" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE381" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF381" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG381" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH381" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI381" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ381" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK381" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 172.</t>
-        </is>
-      </c>
-      <c r="AM381" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN381" t="b">
-        <v>1</v>
       </c>
       <c r="AO381" t="inlineStr">
         <is>
@@ -71312,17 +71218,17 @@
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H382" t="inlineStr">
@@ -71361,76 +71267,170 @@
       <c r="O382" t="n">
         <v>0</v>
       </c>
-      <c r="R382" t="n">
-        <v>0</v>
-      </c>
-      <c r="S382" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U382" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_172</t>
+        </is>
+      </c>
+      <c r="V382" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_172</t>
+        </is>
+      </c>
+      <c r="W382" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X382" t="inlineStr">
+        <is>
+          <t>German measles</t>
+        </is>
+      </c>
+      <c r="Y382" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z382" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA382" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB382" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC382" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD382" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE382" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF382" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG382" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH382" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI382" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ382" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK382" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 172.</t>
+        </is>
+      </c>
+      <c r="AM382" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN382" t="b">
+        <v>1</v>
       </c>
       <c r="AO382" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP382" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ382" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR382" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS382" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS382" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_172</t>
+        </is>
+      </c>
       <c r="AT382" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU382" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV382" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW382" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX382" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY382" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ382" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA382" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB382" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC382" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -71462,12 +71462,12 @@
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H383" t="inlineStr">
@@ -71492,7 +71492,7 @@
       </c>
       <c r="L383" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M383" t="inlineStr">
@@ -71506,9 +71506,6 @@
       <c r="O383" t="n">
         <v>0</v>
       </c>
-      <c r="P383" t="n">
-        <v>0</v>
-      </c>
       <c r="R383" t="n">
         <v>0</v>
       </c>
@@ -71517,82 +71514,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U383" t="inlineStr">
-        <is>
-          <t>SER_JP_RUBELLA_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA383" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO383" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP383" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ383" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS383" t="inlineStr">
-        <is>
-          <t>SER_JP_RUBELLA_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR383" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS383" t="inlineStr"/>
       <c r="AT383" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU383" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV383" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW383" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX383" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY383" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ383" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA383" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB383" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC383" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -71619,7 +71602,7 @@
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F384" t="inlineStr">
@@ -71671,98 +71654,23 @@
       <c r="P384" t="n">
         <v>0</v>
       </c>
+      <c r="R384" t="n">
+        <v>0</v>
+      </c>
+      <c r="S384" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U384" t="inlineStr">
         <is>
           <t>SER_JP_RUBELLA_WEEKLY</t>
         </is>
       </c>
-      <c r="V384" t="inlineStr">
-        <is>
-          <t>SER_JP_RUBELLA_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W384" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X384" t="inlineStr">
-        <is>
-          <t>Rubella</t>
-        </is>
-      </c>
-      <c r="Y384" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z384" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA384" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB384" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC384" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD384" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE384" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF384" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG384" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH384" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI384" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ384" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK384" t="inlineStr">
-        <is>
-          <t>Japan NIID rubella notifications, excluding congenital rubella syndrome.</t>
-        </is>
-      </c>
-      <c r="AM384" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN384" t="b">
-        <v>1</v>
       </c>
       <c r="AO384" t="inlineStr">
         <is>
@@ -71856,17 +71764,17 @@
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H385" t="inlineStr">
@@ -71908,12 +71816,34 @@
       <c r="P385" t="n">
         <v>0</v>
       </c>
-      <c r="R385" t="n">
-        <v>0</v>
-      </c>
-      <c r="S385" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U385" t="inlineStr">
+        <is>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V385" t="inlineStr">
+        <is>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W385" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X385" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="Y385" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z385" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA385" t="inlineStr">
@@ -71921,6 +71851,64 @@
           <t>weekly</t>
         </is>
       </c>
+      <c r="AB385" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC385" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD385" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE385" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF385" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG385" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH385" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI385" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ385" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK385" t="inlineStr">
+        <is>
+          <t>Japan NIID rubella notifications, excluding congenital rubella syndrome.</t>
+        </is>
+      </c>
+      <c r="AM385" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN385" t="b">
+        <v>1</v>
+      </c>
       <c r="AO385" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -71928,7 +71916,7 @@
       </c>
       <c r="AP385" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ385" t="inlineStr">
@@ -71938,55 +71926,55 @@
       </c>
       <c r="AS385" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_RUBELLA; SER_SG_HIST_RUBELLA</t>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
         </is>
       </c>
       <c r="AT385" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU385" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV385" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW385" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX385" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY385" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ385" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA385" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB385" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC385" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -72013,7 +72001,7 @@
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F386" t="inlineStr">
@@ -72065,98 +72053,18 @@
       <c r="P386" t="n">
         <v>0</v>
       </c>
-      <c r="U386" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_RUBELLA</t>
-        </is>
-      </c>
-      <c r="V386" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_RUBELLA</t>
-        </is>
-      </c>
-      <c r="W386" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X386" t="inlineStr">
-        <is>
-          <t>Rubella</t>
-        </is>
-      </c>
-      <c r="Y386" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z386" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R386" t="n">
+        <v>0</v>
+      </c>
+      <c r="S386" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA386" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB386" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC386" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD386" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE386" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF386" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG386" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH386" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI386" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ386" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK386" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM386" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN386" t="b">
-        <v>1</v>
       </c>
       <c r="AO386" t="inlineStr">
         <is>
@@ -72222,6 +72130,1036 @@
         </is>
       </c>
       <c r="BC386" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>D040</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>rubella</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>D040</t>
+        </is>
+      </c>
+      <c r="I387" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="J387" t="inlineStr">
+        <is>
+          <t>风疹</t>
+        </is>
+      </c>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L387" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M387" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N387" t="n">
+        <v>0</v>
+      </c>
+      <c r="O387" t="n">
+        <v>0</v>
+      </c>
+      <c r="P387" t="n">
+        <v>0</v>
+      </c>
+      <c r="U387" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_RUBELLA</t>
+        </is>
+      </c>
+      <c r="V387" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_RUBELLA</t>
+        </is>
+      </c>
+      <c r="W387" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X387" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="Y387" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z387" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA387" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB387" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC387" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD387" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE387" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF387" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG387" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH387" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI387" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ387" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK387" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM387" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN387" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO387" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP387" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ387" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS387" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_RUBELLA; SER_SG_HIST_RUBELLA</t>
+        </is>
+      </c>
+      <c r="AT387" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU387" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV387" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW387" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX387" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY387" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ387" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA387" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB387" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC387" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>D040</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>rubella</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>D040</t>
+        </is>
+      </c>
+      <c r="I388" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="J388" t="inlineStr">
+        <is>
+          <t>风疹</t>
+        </is>
+      </c>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L388" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M388" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N388" t="n">
+        <v>0</v>
+      </c>
+      <c r="O388" t="n">
+        <v>0</v>
+      </c>
+      <c r="P388" t="n">
+        <v>0</v>
+      </c>
+      <c r="R388" t="n">
+        <v>0</v>
+      </c>
+      <c r="S388" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U388" t="inlineStr">
+        <is>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA388" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO388" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP388" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ388" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS388" t="inlineStr">
+        <is>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT388" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU388" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV388" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW388" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX388" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY388" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ388" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA388" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB388" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC388" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>D040</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>rubella</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H389" t="inlineStr">
+        <is>
+          <t>D040</t>
+        </is>
+      </c>
+      <c r="I389" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="J389" t="inlineStr">
+        <is>
+          <t>风疹</t>
+        </is>
+      </c>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L389" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M389" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N389" t="n">
+        <v>0</v>
+      </c>
+      <c r="O389" t="n">
+        <v>0</v>
+      </c>
+      <c r="P389" t="n">
+        <v>0</v>
+      </c>
+      <c r="U389" t="inlineStr">
+        <is>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V389" t="inlineStr">
+        <is>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W389" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X389" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="Y389" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z389" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA389" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB389" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC389" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD389" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE389" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF389" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG389" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH389" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI389" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ389" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK389" t="inlineStr">
+        <is>
+          <t>Japan NIID rubella notifications, excluding congenital rubella syndrome.</t>
+        </is>
+      </c>
+      <c r="AM389" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN389" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO389" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP389" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ389" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS389" t="inlineStr">
+        <is>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT389" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU389" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV389" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW389" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX389" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY389" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ389" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA389" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB389" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC389" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>D040</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>rubella</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>D040</t>
+        </is>
+      </c>
+      <c r="I390" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="J390" t="inlineStr">
+        <is>
+          <t>风疹</t>
+        </is>
+      </c>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L390" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M390" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N390" t="n">
+        <v>0</v>
+      </c>
+      <c r="O390" t="n">
+        <v>0</v>
+      </c>
+      <c r="P390" t="n">
+        <v>0</v>
+      </c>
+      <c r="R390" t="n">
+        <v>0</v>
+      </c>
+      <c r="S390" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA390" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO390" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP390" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ390" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS390" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_RUBELLA; SER_SG_HIST_RUBELLA</t>
+        </is>
+      </c>
+      <c r="AT390" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU390" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV390" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW390" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX390" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY390" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ390" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA390" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB390" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC390" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>D040</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>rubella</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>D040</t>
+        </is>
+      </c>
+      <c r="I391" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="J391" t="inlineStr">
+        <is>
+          <t>风疹</t>
+        </is>
+      </c>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L391" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M391" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N391" t="n">
+        <v>0</v>
+      </c>
+      <c r="O391" t="n">
+        <v>0</v>
+      </c>
+      <c r="P391" t="n">
+        <v>0</v>
+      </c>
+      <c r="U391" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_RUBELLA</t>
+        </is>
+      </c>
+      <c r="V391" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_RUBELLA</t>
+        </is>
+      </c>
+      <c r="W391" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X391" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="Y391" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z391" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA391" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB391" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC391" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD391" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE391" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF391" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG391" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH391" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI391" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ391" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK391" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM391" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN391" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO391" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP391" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ391" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS391" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_RUBELLA; SER_SG_HIST_RUBELLA</t>
+        </is>
+      </c>
+      <c r="AT391" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU391" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV391" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW391" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX391" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY391" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ391" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA391" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB391" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC391" t="inlineStr">
         <is>
           <t>official_csv_and_workbook</t>
         </is>
@@ -72260,7 +73198,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -72343,7 +73281,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>233</v>
+        <v>236</v>
       </c>
     </row>
     <row r="10">
@@ -72353,7 +73291,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>385</v>
+        <v>390</v>
       </c>
     </row>
     <row r="11">
@@ -72373,7 +73311,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d040/2026-2029.xlsx
+++ b/diseases/d040/2026-2029.xlsx
@@ -76245,6 +76245,1347 @@
         </is>
       </c>
     </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>D040</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>rubella</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>D040</t>
+        </is>
+      </c>
+      <c r="I408" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="J408" t="inlineStr">
+        <is>
+          <t>风疹</t>
+        </is>
+      </c>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L408" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M408" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N408" t="n">
+        <v>0</v>
+      </c>
+      <c r="O408" t="n">
+        <v>0</v>
+      </c>
+      <c r="P408" t="n">
+        <v>0</v>
+      </c>
+      <c r="R408" t="n">
+        <v>0</v>
+      </c>
+      <c r="S408" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U408" t="inlineStr">
+        <is>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA408" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO408" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP408" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ408" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS408" t="inlineStr">
+        <is>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT408" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU408" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV408" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW408" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX408" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY408" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ408" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA408" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB408" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC408" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>D040</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>rubella</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>D040</t>
+        </is>
+      </c>
+      <c r="I409" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="J409" t="inlineStr">
+        <is>
+          <t>风疹</t>
+        </is>
+      </c>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L409" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M409" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N409" t="n">
+        <v>0</v>
+      </c>
+      <c r="O409" t="n">
+        <v>0</v>
+      </c>
+      <c r="P409" t="n">
+        <v>0</v>
+      </c>
+      <c r="U409" t="inlineStr">
+        <is>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V409" t="inlineStr">
+        <is>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W409" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X409" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="Y409" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z409" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA409" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB409" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC409" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD409" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE409" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF409" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG409" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH409" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI409" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ409" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK409" t="inlineStr">
+        <is>
+          <t>Japan NIID rubella notifications, excluding congenital rubella syndrome.</t>
+        </is>
+      </c>
+      <c r="AM409" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN409" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO409" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP409" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ409" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS409" t="inlineStr">
+        <is>
+          <t>SER_JP_RUBELLA_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT409" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU409" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV409" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW409" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX409" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY409" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ409" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA409" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB409" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC409" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>D040</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>rubella</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H410" t="inlineStr">
+        <is>
+          <t>D040</t>
+        </is>
+      </c>
+      <c r="I410" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="J410" t="inlineStr">
+        <is>
+          <t>风疹</t>
+        </is>
+      </c>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L410" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M410" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N410" t="n">
+        <v>0</v>
+      </c>
+      <c r="O410" t="n">
+        <v>0</v>
+      </c>
+      <c r="P410" t="n">
+        <v>0</v>
+      </c>
+      <c r="R410" t="n">
+        <v>0</v>
+      </c>
+      <c r="S410" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA410" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO410" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP410" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ410" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS410" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_RUBELLA; SER_SG_HIST_RUBELLA</t>
+        </is>
+      </c>
+      <c r="AT410" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU410" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV410" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW410" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX410" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY410" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ410" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA410" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB410" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC410" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>D040</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>rubella</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>D040</t>
+        </is>
+      </c>
+      <c r="I411" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="J411" t="inlineStr">
+        <is>
+          <t>风疹</t>
+        </is>
+      </c>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L411" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M411" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N411" t="n">
+        <v>0</v>
+      </c>
+      <c r="O411" t="n">
+        <v>0</v>
+      </c>
+      <c r="P411" t="n">
+        <v>0</v>
+      </c>
+      <c r="U411" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_RUBELLA</t>
+        </is>
+      </c>
+      <c r="V411" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_RUBELLA</t>
+        </is>
+      </c>
+      <c r="W411" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X411" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="Y411" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z411" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA411" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB411" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC411" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD411" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE411" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF411" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG411" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH411" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI411" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ411" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK411" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM411" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN411" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO411" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP411" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ411" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS411" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_RUBELLA; SER_SG_HIST_RUBELLA</t>
+        </is>
+      </c>
+      <c r="AT411" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU411" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV411" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW411" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX411" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY411" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ411" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA411" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB411" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC411" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>D040</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>rubella</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>D040</t>
+        </is>
+      </c>
+      <c r="I412" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="J412" t="inlineStr">
+        <is>
+          <t>风疹</t>
+        </is>
+      </c>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L412" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M412" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N412" t="n">
+        <v>0</v>
+      </c>
+      <c r="O412" t="n">
+        <v>0</v>
+      </c>
+      <c r="R412" t="n">
+        <v>0</v>
+      </c>
+      <c r="S412" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U412" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_172</t>
+        </is>
+      </c>
+      <c r="AA412" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO412" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP412" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ412" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR412" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS412" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_172</t>
+        </is>
+      </c>
+      <c r="AT412" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU412" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV412" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW412" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX412" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY412" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ412" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA412" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB412" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC412" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>D040</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>rubella</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>D040</t>
+        </is>
+      </c>
+      <c r="I413" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="J413" t="inlineStr">
+        <is>
+          <t>风疹</t>
+        </is>
+      </c>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L413" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M413" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N413" t="n">
+        <v>0</v>
+      </c>
+      <c r="O413" t="n">
+        <v>0</v>
+      </c>
+      <c r="U413" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_172</t>
+        </is>
+      </c>
+      <c r="V413" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_172</t>
+        </is>
+      </c>
+      <c r="W413" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X413" t="inlineStr">
+        <is>
+          <t>German measles</t>
+        </is>
+      </c>
+      <c r="Y413" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z413" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA413" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB413" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC413" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD413" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE413" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF413" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG413" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH413" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI413" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ413" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK413" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 172.</t>
+        </is>
+      </c>
+      <c r="AM413" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN413" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO413" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP413" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ413" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR413" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS413" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_172</t>
+        </is>
+      </c>
+      <c r="AT413" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU413" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV413" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW413" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX413" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY413" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ413" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA413" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB413" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC413" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>D040</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>rubella</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>D040</t>
+        </is>
+      </c>
+      <c r="I414" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="J414" t="inlineStr">
+        <is>
+          <t>风疹</t>
+        </is>
+      </c>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L414" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M414" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N414" t="n">
+        <v>0</v>
+      </c>
+      <c r="O414" t="n">
+        <v>0</v>
+      </c>
+      <c r="R414" t="n">
+        <v>0</v>
+      </c>
+      <c r="S414" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO414" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP414" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR414" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS414" t="inlineStr"/>
+      <c r="AT414" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU414" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV414" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW414" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX414" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY414" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ414" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA414" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB414" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC414" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -76278,7 +77619,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -76361,7 +77702,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>244</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10">
@@ -76371,7 +77712,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>406</v>
+        <v>413</v>
       </c>
     </row>
     <row r="11">
@@ -76391,7 +77732,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13">
